--- a/data-source/技能数据.xlsx
+++ b/data-source/技能数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B8B9F1-8A84-44A9-8B8E-3A5015044F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF8E57C-FB8A-4442-978E-3E88A85F0FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F03E0F5E-A49D-457A-ADAE-8FAE4055FE2C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="282">
   <si>
     <r>
       <t>被攻击时有</t>
@@ -1415,15 +1415,6 @@
     <t>Lv1-Lv10：游商</t>
   </si>
   <si>
-    <t>Lv1-Lv10：大车炮台被弃者地下城；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：大车炮台/被弃者地下城；</t>
-  </si>
-  <si>
-    <t>Lv5-Lv10：大车炮台；Lv1-Lv10：被弃者地下城；</t>
-  </si>
-  <si>
     <t>Lv1-Lv10：游商/酷吏地下城</t>
   </si>
   <si>
@@ -1466,15 +1457,6 @@
     <t>Lv1-Lv4：4级图；Lv1-Lv8：5级图/城堡；Lv5-Lv10：大车炮台；Lv6-Lv10：酷吏地下城</t>
   </si>
   <si>
-    <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士；Lv1-Lv10: 古人墓穴/大车炮台/被弃者地下城；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：被弃者地下城/地下神祠/堕落骑士；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士；Lv1-Lv10：被弃者地下城；</t>
-  </si>
-  <si>
     <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士</t>
   </si>
   <si>
@@ -1484,57 +1466,9 @@
     <t>Lv1-Lv5：死灵法师的巢穴；Lv1-Lv10: 古人墓穴/西方银矿/被诅咒的天文台；</t>
   </si>
   <si>
-    <t>Lv1：野蛮人营地；Lv1-Lv10: 古人墓穴/被弃者地下城；</t>
-  </si>
-  <si>
-    <t>Lv1：哈利德/哈特/弗拉格纳/1-3级图/地下神祠/墓地之夜；Lv1-Lv2：4级图/5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：哈利德/哈特/弗拉格纳/1-3级图/地下神祠/墓地之夜；Lv2-Lv3：4级图/5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：地下神祠/墓地之夜；Lv1-Lv3：哈利德/哈特/弗拉格纳/1-3级图；Lv3-Lv4：4级图/5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：地下神祠/墓地之夜；Lv1-Lv4：哈利德/哈特/弗拉格纳/1-3级图；Lv4-Lv5：4级图/5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：1-3级图；Lv1-Lv4：墓地之夜；Lv4-Lv7：被弃者地下城；Lv5-Lv7：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：1-3级图；Lv1-Lv4：墓地之夜；Lv5-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；Lv1-Lv10：被诅咒的天文台</t>
-  </si>
-  <si>
-    <t>Lv1-Lv4：1-3级图/墓地之夜；Lv3-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜；Lv1-Lv4：1-3级图；Lv5-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；Lv1-Lv10：大车炮台；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜；Lv1-Lv4：1-3级图；Lv5-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv7-Lv8：商人护送；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv4：1-3级图/墓地之夜；Lv3-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv8：4级图；Lv5-Lv10：5级图/城堡；Lv1-Lv10：大车炮台；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv3：1-3级图/墓地之夜；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv10：被弃者地下城；Lv3-Lv5：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv6：4级图；Lv5-Lv8：5级图/城堡；Lv1-Lv10：被诅咒的天文台</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：1-3级图；Lv1-Lv4：墓地之夜；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv4：1-3级图/墓地之夜；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
     <t>Lv1-Lv5：死灵法师的巢穴；Lv1-Lv10：西方银矿/继母艾莎；</t>
   </si>
   <si>
-    <t>Lv1-Lv4：1-3级图/墓地之夜；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv4：1-3级图/铜矿/墓地之夜；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
     <t>Lv1-Lv4：1-3级图/墓地之夜；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv8：哈特/弗拉格纳；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
   </si>
   <si>
@@ -1542,42 +1476,6 @@
   </si>
   <si>
     <t>Lv1-Lv5：死灵法师的巢穴；Lv1-Lv10: 古人墓穴/西方银矿/继母艾莎；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv4：1-3级图/墓地之夜；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv10：被弃者地下城；Lv3-Lv6：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv7：4级图；Lv5-Lv8：5级图/城堡；Lv1-Lv10：大车炮台；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv4：1-3级图/墓地之夜；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；Lv1-Lv10：大车炮台；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv3：1-3级图/墓地之夜；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv5：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv6：4级图；Lv3-Lv10：被弃者地下城；Lv5-Lv8：城堡</t>
-  </si>
-  <si>
-    <t>Lv1-Lv3：1-3级图/墓地之夜；Lv3-Lv5：哈利德/哈特/弗拉格纳/被弃者地下城/叛徒地下墓穴/继母艾莎；Lv4-Lv5：4级图；Lv1-Lv5：地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv3：1-3级图/墓地之夜；Lv3-Lv5：哈利德/哈特/弗拉格纳/被弃者地下城/叛徒地下墓穴/继母艾莎；Lv4-Lv5：4级图；Lv1-Lv5：地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；Lv1-Lv10：被诅咒的天文台</t>
-  </si>
-  <si>
-    <t>Lv1-Lv3：1-3级图/墓地之夜；Lv3-Lv5：被弃者地下城/叛徒地下墓穴/继母艾莎；Lv4-Lv5：4级图；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜；Lv1-Lv4：1-3级图；Lv4-Lv5：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv5：被弃者地下城/地下神祠；Lv1-Lv6：哈利德/哈特/弗拉格纳；Lv5-Lv6：4级图/5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜；Lv1-Lv4：1-3级图；Lv5-Lv6：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv5-Lv7：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜；Lv1-Lv4：1-3级图；Lv5-Lv6：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv5-Lv8：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜；Lv1-Lv4：1-3级图；Lv5-Lv6：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv1-Lv9：被弃者地下城；Lv5-Lv8：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜；Lv1-Lv4：1-3级图；Lv5-Lv6：叛徒地下墓穴/继母艾莎；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv5-Lv10：大车炮台/酷吏地下城；Lv5-Lv8：5级图/城堡；Lv1-Lv9：被弃者地下城；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜；Lv1-Lv4：1-3级图；Lv5-Lv6：叛徒地下墓穴/继母艾莎；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：大车炮台/酷吏地下城；Lv5-Lv8：5级图/城堡；Lv1-Lv9：被弃者地下城；</t>
   </si>
   <si>
     <t>Lv5-Lv10：大车炮台；Lv1-Lv9：继母艾莎；Lv6-Lv10：酷吏地下城</t>
@@ -1603,6 +1501,120 @@
       </rPr>
       <t>%闪避概率</t>
     </r>
+  </si>
+  <si>
+    <t>Lv1：哈利德/哈特/弗拉格纳/1-3级图/地下神祠/墓地之夜/小型被弃者地窖/被弃者地窖；Lv1-Lv2：4级图/5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：哈利德/哈特/弗拉格纳/1-3级图/地下神祠/墓地之夜/小型被弃者地窖/被弃者地窖；Lv2-Lv3：4级图/5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：地下神祠/墓地之夜/小型被弃者地窖；Lv1-Lv3：哈利德/哈特/弗拉格纳/1-3级图/被弃者地窖；Lv3-Lv4：4级图/5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：地下神祠/墓地之夜/小型被弃者地窖；Lv1-Lv4：哈利德/哈特/弗拉格纳/1-3级图/被弃者地窖；Lv4-Lv5：4级图/5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：1-3级图/小型被弃者地窖/被弃者地窖；Lv1-Lv4：墓地之夜；Lv4-Lv7：被弃者地下城/大型被弃者地窖；Lv5-Lv7：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：1-3级图/小型被弃者地窖/被弃者地窖；Lv1-Lv4：墓地之夜；Lv5-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；Lv1-Lv10：被诅咒的天文台</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；Lv1-Lv10：大车炮台；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv7-Lv8：商人护送；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv8：4级图；Lv5-Lv10：5级图/城堡；Lv1-Lv10：大车炮台；</t>
+  </si>
+  <si>
+    <t>Lv1：野蛮人营地；Lv1-Lv10: 古人墓穴/被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv10：被弃者地下城/大型被弃者地窖；Lv3-Lv5：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv6：4级图；Lv5-Lv8：5级图/城堡；Lv1-Lv10：被诅咒的天文台</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：1-3级图/小型被弃者地窖/被弃者地窖；Lv1-Lv4：墓地之夜；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：大车炮台/被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士；Lv1-Lv10：被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：被弃者地下城/地下神祠/堕落骑士/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/铜矿/墓地之夜/被弃者地窖；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv8：小型被弃者地窖；Lv1-Lv10：被弃者地窖/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv8：小型被弃者地窖；Lv1-Lv10：继母艾莎/被弃者地窖/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv8：小型被弃者地窖/被弃者地窖；Lv1-Lv10：继母艾莎/大型被弃者地窖</t>
+  </si>
+  <si>
+    <t>Lv1-Lv4：被弃者地窖；Lv1-Lv10：继母艾莎/大型被弃者地窖</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv10：被弃者地下城/大型被弃者地窖；Lv3-Lv6：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv7：4级图；Lv5-Lv8：5级图/城堡；Lv1-Lv10：大车炮台；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；Lv1-Lv10：大车炮台；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv5：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv6：4级图；Lv3-Lv10：被弃者地下城；Lv5-Lv8：城堡；Lv3-Lv10：大型被弃者地窖</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：大车炮台被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士；Lv1-Lv10: 古人墓穴/大车炮台/被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：哈利德/哈特/弗拉格纳/被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：哈利德/哈特/弗拉格纳/被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；Lv1-Lv10：被诅咒的天文台</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv4-Lv5：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv5：被弃者地下城/地下神祠/大型被弃者地窖；Lv1-Lv6：哈利德/哈特/弗拉格纳；Lv5-Lv6：4级图/5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv5-Lv7：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv5-Lv8：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv1-Lv9：被弃者地下城/大型被弃者地窖；Lv5-Lv8：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：叛徒地下墓穴/继母艾莎；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv5-Lv10：大车炮台/酷吏地下城；Lv5-Lv8：5级图/城堡；Lv1-Lv9：被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：叛徒地下墓穴/继母艾莎；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：大车炮台/酷吏地下城；Lv5-Lv8：5级图/城堡；Lv1-Lv9：被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv5-Lv10：大车炮台；Lv1-Lv10：被弃者地下城/大型被弃者地窖；</t>
   </si>
 </sst>
 </file>
@@ -3172,7 +3184,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="27.75">
+    <row r="3" spans="2:21" ht="41.65">
       <c r="B3" s="81" t="s">
         <v>144</v>
       </c>
@@ -3215,7 +3227,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="27.75">
+    <row r="4" spans="2:21" ht="41.65">
       <c r="B4" s="82" t="s">
         <v>143</v>
       </c>
@@ -3258,7 +3270,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="27.75">
+    <row r="5" spans="2:21" ht="41.65">
       <c r="B5" s="82" t="s">
         <v>142</v>
       </c>
@@ -3283,7 +3295,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="6" spans="2:21" ht="27.75">
+    <row r="6" spans="2:21" ht="41.65">
       <c r="B6" s="82" t="s">
         <v>140</v>
       </c>
@@ -3386,10 +3398,10 @@
         <v>4.2</v>
       </c>
       <c r="R7" s="68" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="8" spans="2:21" ht="27.75">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21" ht="41.65">
       <c r="B8" s="82" t="s">
         <v>138</v>
       </c>
@@ -3442,7 +3454,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="9" spans="2:21" ht="27.75">
+    <row r="9" spans="2:21" ht="41.65">
       <c r="B9" s="82" t="s">
         <v>137</v>
       </c>
@@ -3495,7 +3507,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="10" spans="2:21" ht="27.75">
+    <row r="10" spans="2:21" ht="41.65">
       <c r="B10" s="82" t="s">
         <v>136</v>
       </c>
@@ -3598,7 +3610,7 @@
         <v>15</v>
       </c>
       <c r="R11" s="68" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="2:21">
@@ -3999,7 +4011,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="22" spans="2:20">
+    <row r="22" spans="2:20" ht="27.75">
       <c r="B22" s="108" t="s">
         <v>126</v>
       </c>
@@ -4030,7 +4042,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="23" spans="2:20">
+    <row r="23" spans="2:20" ht="27.75">
       <c r="B23" s="108" t="s">
         <v>125</v>
       </c>
@@ -4061,7 +4073,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="24" spans="2:20">
+    <row r="24" spans="2:20" ht="27.75">
       <c r="B24" s="108" t="s">
         <v>124</v>
       </c>
@@ -4094,7 +4106,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="25" spans="2:20">
+    <row r="25" spans="2:20" ht="27.75">
       <c r="B25" s="108" t="s">
         <v>123</v>
       </c>
@@ -4127,7 +4139,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="26" spans="2:20">
+    <row r="26" spans="2:20" ht="27.75">
       <c r="B26" s="108" t="s">
         <v>122</v>
       </c>
@@ -4192,7 +4204,7 @@
       <c r="P27" s="35"/>
       <c r="Q27" s="35"/>
       <c r="R27" s="68" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28" spans="2:20" ht="27.75">
@@ -4227,7 +4239,7 @@
       <c r="P28" s="35"/>
       <c r="Q28" s="35"/>
       <c r="R28" s="68" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="2:20" ht="27.75">
@@ -4262,10 +4274,10 @@
       <c r="P29" s="35"/>
       <c r="Q29" s="35"/>
       <c r="R29" s="68" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="30" spans="2:20" ht="28.15" thickBot="1">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="30" spans="2:20" ht="42" thickBot="1">
       <c r="B30" s="108" t="s">
         <v>118</v>
       </c>
@@ -4299,10 +4311,10 @@
       <c r="P30" s="35"/>
       <c r="Q30" s="35"/>
       <c r="R30" s="68" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="31" spans="2:20" ht="28.15" thickBot="1">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20" ht="42" thickBot="1">
       <c r="B31" s="108" t="s">
         <v>117</v>
       </c>
@@ -4338,7 +4350,7 @@
       <c r="P31" s="35"/>
       <c r="Q31" s="35"/>
       <c r="R31" s="68" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="T31" s="52"/>
     </row>
@@ -4378,10 +4390,10 @@
       <c r="P32" s="35"/>
       <c r="Q32" s="35"/>
       <c r="R32" s="68" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" ht="27.75">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" ht="41.65">
       <c r="B33" s="108" t="s">
         <v>115</v>
       </c>
@@ -4417,7 +4429,7 @@
       <c r="P33" s="35"/>
       <c r="Q33" s="35"/>
       <c r="R33" s="68" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" spans="2:18" ht="27.75">
@@ -4458,7 +4470,7 @@
       <c r="P34" s="35"/>
       <c r="Q34" s="35"/>
       <c r="R34" s="68" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35" spans="2:18">
@@ -4564,7 +4576,7 @@
         <v>15</v>
       </c>
       <c r="R36" s="68" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="37" spans="2:18">
@@ -4617,10 +4629,10 @@
         <v>15</v>
       </c>
       <c r="R37" s="71" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="38" spans="2:18" ht="27.75">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" ht="41.65">
       <c r="B38" s="108" t="s">
         <v>111</v>
       </c>
@@ -4670,7 +4682,7 @@
         <v>15</v>
       </c>
       <c r="R38" s="68" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39" spans="2:18">
@@ -4723,7 +4735,7 @@
         <v>15</v>
       </c>
       <c r="R39" s="71" t="s">
-        <v>275</v>
+        <v>241</v>
       </c>
     </row>
     <row r="40" spans="2:18">
@@ -4776,7 +4788,7 @@
         <v>15</v>
       </c>
       <c r="R40" s="71" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="2:18">
@@ -4829,7 +4841,7 @@
         <v>15</v>
       </c>
       <c r="R41" s="71" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="2:18">
@@ -4882,7 +4894,7 @@
         <v>0.3</v>
       </c>
       <c r="R42" s="71" t="s">
-        <v>222</v>
+        <v>281</v>
       </c>
     </row>
     <row r="43" spans="2:18">
@@ -4935,7 +4947,7 @@
         <v>0.4</v>
       </c>
       <c r="R43" s="71" t="s">
-        <v>222</v>
+        <v>281</v>
       </c>
     </row>
     <row r="44" spans="2:18" ht="14.65" thickBot="1">
@@ -5062,7 +5074,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="2:18" ht="28.5">
+    <row r="47" spans="2:18" ht="42.75">
       <c r="B47" s="85" t="s">
         <v>104</v>
       </c>
@@ -5102,10 +5114,10 @@
       <c r="P47" s="35"/>
       <c r="Q47" s="35"/>
       <c r="R47" s="73" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18" ht="28.5">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" ht="42.75">
       <c r="B48" s="86" t="s">
         <v>103</v>
       </c>
@@ -5145,10 +5157,10 @@
       <c r="P48" s="35"/>
       <c r="Q48" s="35"/>
       <c r="R48" s="73" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="49" spans="2:18" ht="28.5">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="49" spans="2:18" ht="42.75">
       <c r="B49" s="86" t="s">
         <v>102</v>
       </c>
@@ -5188,10 +5200,10 @@
       <c r="P49" s="35"/>
       <c r="Q49" s="35"/>
       <c r="R49" s="73" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="50" spans="2:18" ht="28.5">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="50" spans="2:18" ht="42.75">
       <c r="B50" s="86" t="s">
         <v>101</v>
       </c>
@@ -5231,10 +5243,10 @@
       <c r="P50" s="35"/>
       <c r="Q50" s="35"/>
       <c r="R50" s="73" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="51" spans="2:18" ht="28.5">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="51" spans="2:18" ht="42.75">
       <c r="B51" s="86" t="s">
         <v>100</v>
       </c>
@@ -5274,10 +5286,10 @@
       <c r="P51" s="35"/>
       <c r="Q51" s="35"/>
       <c r="R51" s="73" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="52" spans="2:18" ht="28.5">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="52" spans="2:18" ht="42.75">
       <c r="B52" s="86" t="s">
         <v>99</v>
       </c>
@@ -5317,10 +5329,10 @@
       <c r="P52" s="35"/>
       <c r="Q52" s="35"/>
       <c r="R52" s="73" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="53" spans="2:18" ht="28.5">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="53" spans="2:18" ht="42.75">
       <c r="B53" s="86" t="s">
         <v>98</v>
       </c>
@@ -5360,10 +5372,10 @@
       <c r="P53" s="35"/>
       <c r="Q53" s="35"/>
       <c r="R53" s="73" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="54" spans="2:18" ht="28.5">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="54" spans="2:18" ht="42.75">
       <c r="B54" s="86" t="s">
         <v>97</v>
       </c>
@@ -5403,7 +5415,7 @@
       <c r="P54" s="35"/>
       <c r="Q54" s="35"/>
       <c r="R54" s="73" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="55" spans="2:18">
@@ -5438,7 +5450,7 @@
       <c r="P55" s="35"/>
       <c r="Q55" s="35"/>
       <c r="R55" s="71" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="56" spans="2:18">
@@ -5473,7 +5485,7 @@
       <c r="P56" s="35"/>
       <c r="Q56" s="35"/>
       <c r="R56" s="71" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="57" spans="2:18">
@@ -5508,7 +5520,7 @@
       <c r="P57" s="35"/>
       <c r="Q57" s="35"/>
       <c r="R57" s="71" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="58" spans="2:18" ht="14.65" thickBot="1">
@@ -5543,7 +5555,7 @@
       <c r="P58" s="48"/>
       <c r="Q58" s="48"/>
       <c r="R58" s="72" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="59" spans="2:18" ht="15" thickTop="1" thickBot="1">
@@ -5657,7 +5669,7 @@
       <c r="P61" s="35"/>
       <c r="Q61" s="35"/>
       <c r="R61" s="73" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="62" spans="2:18" ht="28.5">
@@ -5700,7 +5712,7 @@
       <c r="P62" s="35"/>
       <c r="Q62" s="35"/>
       <c r="R62" s="73" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" spans="2:18" ht="28.5">
@@ -5743,7 +5755,7 @@
       <c r="P63" s="35"/>
       <c r="Q63" s="35"/>
       <c r="R63" s="73" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="64" spans="2:18" ht="28.5">
@@ -5786,7 +5798,7 @@
       <c r="P64" s="35"/>
       <c r="Q64" s="35"/>
       <c r="R64" s="73" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="2:18" ht="28.5">
@@ -5829,7 +5841,7 @@
       <c r="P65" s="35"/>
       <c r="Q65" s="35"/>
       <c r="R65" s="73" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="66" spans="2:18" ht="28.5">
@@ -5872,7 +5884,7 @@
       <c r="P66" s="35"/>
       <c r="Q66" s="35"/>
       <c r="R66" s="73" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="2:18" ht="28.5">
@@ -5915,7 +5927,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="35"/>
       <c r="R67" s="73" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="68" spans="2:18">
@@ -5958,7 +5970,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="35"/>
       <c r="R68" s="71" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69" spans="2:18">
@@ -6001,7 +6013,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
       <c r="R69" s="71" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="70" spans="2:18">
@@ -6044,7 +6056,7 @@
       <c r="P70" s="35"/>
       <c r="Q70" s="35"/>
       <c r="R70" s="71" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="71" spans="2:18">
@@ -6086,7 +6098,9 @@
       <c r="O71" s="35"/>
       <c r="P71" s="35"/>
       <c r="Q71" s="35"/>
-      <c r="R71" s="71"/>
+      <c r="R71" s="71" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="72" spans="2:18">
       <c r="B72" s="101" t="s">
@@ -6127,7 +6141,9 @@
       <c r="O72" s="35"/>
       <c r="P72" s="35"/>
       <c r="Q72" s="35"/>
-      <c r="R72" s="71"/>
+      <c r="R72" s="71" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="73" spans="2:18">
       <c r="B73" s="101" t="s">
@@ -6169,7 +6185,7 @@
       <c r="P73" s="35"/>
       <c r="Q73" s="35"/>
       <c r="R73" s="71" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="74" spans="2:18">
@@ -6212,7 +6228,7 @@
       <c r="P74" s="35"/>
       <c r="Q74" s="35"/>
       <c r="R74" s="71" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="75" spans="2:18">
@@ -6255,7 +6271,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="35"/>
       <c r="R75" s="71" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="76" spans="2:18">
@@ -6298,7 +6314,7 @@
       <c r="P76" s="35"/>
       <c r="Q76" s="35"/>
       <c r="R76" s="71" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="77" spans="2:18">
@@ -6341,7 +6357,7 @@
       <c r="P77" s="35"/>
       <c r="Q77" s="35"/>
       <c r="R77" s="71" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="78" spans="2:18">
@@ -6384,7 +6400,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
       <c r="R78" s="71" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="79" spans="2:18">
@@ -6392,7 +6408,7 @@
         <v>73</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>277</v>
+        <v>243</v>
       </c>
       <c r="D79" s="6">
         <v>2</v>
@@ -6427,7 +6443,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
       <c r="R79" s="71" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80" spans="2:18">
@@ -6470,7 +6486,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
       <c r="R80" s="71" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="81" spans="2:18">
@@ -6513,7 +6529,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
       <c r="R81" s="71" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="82" spans="2:18">
@@ -6556,7 +6572,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
       <c r="R82" s="71" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="83" spans="2:18">
@@ -6599,7 +6615,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
       <c r="R83" s="71" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="84" spans="2:18">
@@ -6642,7 +6658,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
       <c r="R84" s="71" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="85" spans="2:18" ht="28.5">
@@ -6685,7 +6701,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
       <c r="R85" s="73" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="86" spans="2:18" ht="28.5">
@@ -6728,7 +6744,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
       <c r="R86" s="73" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="87" spans="2:18" ht="28.5">
@@ -6771,7 +6787,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
       <c r="R87" s="73" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="88" spans="2:18">
@@ -6814,7 +6830,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
       <c r="R88" s="71" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="89" spans="2:18">
@@ -6857,7 +6873,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
       <c r="R89" s="71" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="90" spans="2:18">
@@ -6986,7 +7002,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
       <c r="R92" s="71" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="93" spans="2:18">
@@ -7029,7 +7045,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
       <c r="R93" s="71" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
     </row>
     <row r="94" spans="2:18">
@@ -7072,7 +7088,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
       <c r="R94" s="71" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
     </row>
     <row r="95" spans="2:18">
@@ -7258,7 +7274,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="100" spans="2:18" ht="28.5">
+    <row r="100" spans="2:18" ht="42.75">
       <c r="B100" s="104" t="s">
         <v>53</v>
       </c>
@@ -7298,7 +7314,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
       <c r="R100" s="73" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="101" spans="2:18">
@@ -7341,10 +7357,10 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
       <c r="R101" s="71" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="102" spans="2:18" ht="28.5">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="102" spans="2:18" ht="42.75">
       <c r="B102" s="105" t="s">
         <v>51</v>
       </c>
@@ -7384,10 +7400,10 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
       <c r="R102" s="73" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="103" spans="2:18" ht="28.5">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="103" spans="2:18" ht="42.75">
       <c r="B103" s="105" t="s">
         <v>50</v>
       </c>
@@ -7427,7 +7443,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
       <c r="R103" s="73" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="104" spans="2:18">
@@ -7470,10 +7486,10 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
       <c r="R104" s="71" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="105" spans="2:18" ht="28.5">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="105" spans="2:18" ht="42.75">
       <c r="B105" s="105" t="s">
         <v>48</v>
       </c>
@@ -7513,10 +7529,10 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
       <c r="R105" s="73" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="106" spans="2:18" ht="28.9" thickBot="1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="106" spans="2:18" ht="43.15" thickBot="1">
       <c r="B106" s="106" t="s">
         <v>47</v>
       </c>
@@ -7556,7 +7572,7 @@
       <c r="P106" s="48"/>
       <c r="Q106" s="48"/>
       <c r="R106" s="74" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="107" spans="2:18" ht="15" thickTop="1" thickBot="1"/>
@@ -7613,7 +7629,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="109" spans="2:18" ht="28.5">
+    <row r="109" spans="2:18" ht="42.75">
       <c r="B109" s="88" t="s">
         <v>45</v>
       </c>
@@ -7653,10 +7669,10 @@
       <c r="P109" s="4"/>
       <c r="Q109" s="43"/>
       <c r="R109" s="73" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="110" spans="2:18" ht="28.5">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="110" spans="2:18" ht="42.75">
       <c r="B110" s="89" t="s">
         <v>44</v>
       </c>
@@ -7706,10 +7722,10 @@
         <v>30</v>
       </c>
       <c r="R110" s="73" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="111" spans="2:18" ht="28.5">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="111" spans="2:18" ht="42.75">
       <c r="B111" s="88" t="s">
         <v>25</v>
       </c>
@@ -7749,7 +7765,7 @@
       <c r="P111" s="4"/>
       <c r="Q111" s="43"/>
       <c r="R111" s="73" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="112" spans="2:18" ht="28.5">
@@ -7792,10 +7808,10 @@
       <c r="P112" s="4"/>
       <c r="Q112" s="43"/>
       <c r="R112" s="73" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="113" spans="2:20" ht="28.5">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="113" spans="2:20" ht="42.75">
       <c r="B113" s="90" t="s">
         <v>42</v>
       </c>
@@ -7835,10 +7851,10 @@
       <c r="P113" s="5"/>
       <c r="Q113" s="45"/>
       <c r="R113" s="73" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="114" spans="2:20" ht="28.5">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="114" spans="2:20" ht="42.75">
       <c r="B114" s="88" t="s">
         <v>43</v>
       </c>
@@ -7878,7 +7894,7 @@
       <c r="P114" s="4"/>
       <c r="Q114" s="43"/>
       <c r="R114" s="73" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="115" spans="2:20">
@@ -7931,7 +7947,7 @@
         <v>0.5</v>
       </c>
       <c r="R115" s="71" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="116" spans="2:20">
@@ -8187,7 +8203,7 @@
       <c r="P120" s="35"/>
       <c r="Q120" s="47"/>
       <c r="R120" s="71" t="s">
-        <v>220</v>
+        <v>270</v>
       </c>
     </row>
     <row r="121" spans="2:20" ht="14.65" thickBot="1">
@@ -8230,7 +8246,7 @@
       <c r="P121" s="48"/>
       <c r="Q121" s="49"/>
       <c r="R121" s="72" t="s">
-        <v>237</v>
+        <v>271</v>
       </c>
     </row>
     <row r="122" spans="2:20" ht="15" thickTop="1" thickBot="1"/>
@@ -8287,7 +8303,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="124" spans="2:20" ht="28.5">
+    <row r="124" spans="2:20" ht="42.75">
       <c r="B124" s="93" t="s">
         <v>24</v>
       </c>
@@ -8327,7 +8343,7 @@
       <c r="P124" s="4"/>
       <c r="Q124" s="43"/>
       <c r="R124" s="63" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="125" spans="2:20" ht="28.5">
@@ -8370,7 +8386,7 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="43"/>
       <c r="R125" s="63" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="126" spans="2:20" ht="28.5">
@@ -8413,7 +8429,7 @@
       <c r="P126" s="4"/>
       <c r="Q126" s="43"/>
       <c r="R126" s="63" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="127" spans="2:20">
@@ -8456,7 +8472,7 @@
       <c r="P127" s="4"/>
       <c r="Q127" s="43"/>
       <c r="R127" s="56" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
     </row>
     <row r="128" spans="2:20">
@@ -8489,7 +8505,7 @@
       <c r="P128" s="4"/>
       <c r="Q128" s="43"/>
       <c r="R128" s="56" t="s">
-        <v>221</v>
+        <v>258</v>
       </c>
     </row>
     <row r="129" spans="2:18">
@@ -8532,7 +8548,7 @@
       <c r="P129" s="4"/>
       <c r="Q129" s="43"/>
       <c r="R129" s="56" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="130" spans="2:18">
@@ -8575,7 +8591,7 @@
       <c r="P130" s="4"/>
       <c r="Q130" s="43"/>
       <c r="R130" s="56" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="131" spans="2:18">
@@ -8681,7 +8697,7 @@
         <v>0.2</v>
       </c>
       <c r="R132" s="56" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="133" spans="2:18">
@@ -8769,22 +8785,22 @@
         <v>0.41</v>
       </c>
       <c r="L134" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="M134" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="N134" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="O134" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="P134" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="Q134" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="R134" s="56" t="s">
         <v>211</v>
@@ -8830,7 +8846,7 @@
       <c r="P135" s="76"/>
       <c r="Q135" s="77"/>
       <c r="R135" s="56" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="136" spans="2:18">
@@ -8908,22 +8924,22 @@
         <v>0.26</v>
       </c>
       <c r="L137" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="M137" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="N137" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="O137" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="P137" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="Q137" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="R137" s="56" t="s">
         <v>211</v>
@@ -8961,22 +8977,22 @@
         <v>1.06</v>
       </c>
       <c r="L138" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="M138" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="N138" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="O138" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="P138" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="Q138" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="R138" s="56" t="s">
         <v>211</v>
@@ -9012,7 +9028,7 @@
       <c r="P139" s="2"/>
       <c r="Q139" s="78"/>
       <c r="R139" s="56" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
     </row>
     <row r="140" spans="2:18">
@@ -9103,19 +9119,19 @@
         <v>0.1</v>
       </c>
       <c r="M141" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="N141" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="O141" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="P141" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="Q141" s="32" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="R141" s="56" t="s">
         <v>215</v>
@@ -9171,7 +9187,7 @@
         <v>0.15</v>
       </c>
       <c r="R142" s="58" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
     </row>
     <row r="143" spans="2:18" ht="14.65" thickTop="1"/>
@@ -9181,6 +9197,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F24FF01B6E691B418AC7A3AA007394EC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2842777d906afb735552f47e63b23c65">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8f43ef-8ea4-412d-9c18-5388ad596486" xmlns:ns4="c1e77170-3c0a-491c-a033-5a7c184eabd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="352f9ab862d979d0253968f43d118292" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
@@ -9399,24 +9432,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53964A40-A6D0-45D9-B1D4-1342A31D1BCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35331C5A-856A-46E2-8755-4FFF5881D9DA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9433,29 +9474,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53964A40-A6D0-45D9-B1D4-1342A31D1BCB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data-source/技能数据.xlsx
+++ b/data-source/技能数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF8E57C-FB8A-4442-978E-3E88A85F0FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9D8BAE-8467-47FB-B785-6FE210316FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F03E0F5E-A49D-457A-ADAE-8FAE4055FE2C}"/>
   </bookViews>
@@ -1621,7 +1621,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1676,6 +1676,12 @@
       <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="16">
@@ -1747,12 +1753,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD8D4CC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1766,6 +1766,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE06666"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC08FE8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2514,7 +2520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2780,37 +2786,25 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2819,19 +2813,32 @@
     <xf numFmtId="0" fontId="8" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2842,6 +2849,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFC08FE8"/>
       <color rgb="FFE06666"/>
       <color rgb="FF8A8579"/>
       <color rgb="FFD8D4CC"/>
@@ -3122,7 +3130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76EA8BDA-DC66-4172-AEE2-6135C3F09C61}">
-  <dimension ref="B1:U143"/>
+  <dimension ref="B1:U150"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
@@ -3898,7 +3906,7 @@
       </c>
     </row>
     <row r="18" spans="2:20">
-      <c r="B18" s="107" t="s">
+      <c r="B18" s="100" t="s">
         <v>130</v>
       </c>
       <c r="C18" s="12" t="s">
@@ -3925,7 +3933,7 @@
       </c>
     </row>
     <row r="19" spans="2:20">
-      <c r="B19" s="108" t="s">
+      <c r="B19" s="101" t="s">
         <v>129</v>
       </c>
       <c r="C19" s="12" t="s">
@@ -3954,7 +3962,7 @@
       </c>
     </row>
     <row r="20" spans="2:20">
-      <c r="B20" s="108" t="s">
+      <c r="B20" s="101" t="s">
         <v>128</v>
       </c>
       <c r="C20" s="12" t="s">
@@ -3983,7 +3991,7 @@
       </c>
     </row>
     <row r="21" spans="2:20">
-      <c r="B21" s="108" t="s">
+      <c r="B21" s="101" t="s">
         <v>127</v>
       </c>
       <c r="C21" s="12" t="s">
@@ -4012,7 +4020,7 @@
       </c>
     </row>
     <row r="22" spans="2:20" ht="27.75">
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="101" t="s">
         <v>126</v>
       </c>
       <c r="C22" s="12" t="s">
@@ -4043,7 +4051,7 @@
       </c>
     </row>
     <row r="23" spans="2:20" ht="27.75">
-      <c r="B23" s="108" t="s">
+      <c r="B23" s="101" t="s">
         <v>125</v>
       </c>
       <c r="C23" s="12" t="s">
@@ -4074,7 +4082,7 @@
       </c>
     </row>
     <row r="24" spans="2:20" ht="27.75">
-      <c r="B24" s="108" t="s">
+      <c r="B24" s="101" t="s">
         <v>124</v>
       </c>
       <c r="C24" s="12" t="s">
@@ -4107,7 +4115,7 @@
       </c>
     </row>
     <row r="25" spans="2:20" ht="27.75">
-      <c r="B25" s="108" t="s">
+      <c r="B25" s="101" t="s">
         <v>123</v>
       </c>
       <c r="C25" s="12" t="s">
@@ -4140,7 +4148,7 @@
       </c>
     </row>
     <row r="26" spans="2:20" ht="27.75">
-      <c r="B26" s="108" t="s">
+      <c r="B26" s="101" t="s">
         <v>122</v>
       </c>
       <c r="C26" s="12" t="s">
@@ -4173,7 +4181,7 @@
       </c>
     </row>
     <row r="27" spans="2:20" ht="27.75">
-      <c r="B27" s="108" t="s">
+      <c r="B27" s="101" t="s">
         <v>121</v>
       </c>
       <c r="C27" s="12" t="s">
@@ -4208,7 +4216,7 @@
       </c>
     </row>
     <row r="28" spans="2:20" ht="27.75">
-      <c r="B28" s="108" t="s">
+      <c r="B28" s="101" t="s">
         <v>120</v>
       </c>
       <c r="C28" s="12" t="s">
@@ -4243,7 +4251,7 @@
       </c>
     </row>
     <row r="29" spans="2:20" ht="27.75">
-      <c r="B29" s="108" t="s">
+      <c r="B29" s="101" t="s">
         <v>119</v>
       </c>
       <c r="C29" s="12" t="s">
@@ -4278,7 +4286,7 @@
       </c>
     </row>
     <row r="30" spans="2:20" ht="42" thickBot="1">
-      <c r="B30" s="108" t="s">
+      <c r="B30" s="101" t="s">
         <v>118</v>
       </c>
       <c r="C30" s="12" t="s">
@@ -4315,7 +4323,7 @@
       </c>
     </row>
     <row r="31" spans="2:20" ht="42" thickBot="1">
-      <c r="B31" s="108" t="s">
+      <c r="B31" s="101" t="s">
         <v>117</v>
       </c>
       <c r="C31" s="12" t="s">
@@ -4355,7 +4363,7 @@
       <c r="T31" s="52"/>
     </row>
     <row r="32" spans="2:20">
-      <c r="B32" s="108" t="s">
+      <c r="B32" s="101" t="s">
         <v>116</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -4394,7 +4402,7 @@
       </c>
     </row>
     <row r="33" spans="2:18" ht="41.65">
-      <c r="B33" s="108" t="s">
+      <c r="B33" s="101" t="s">
         <v>115</v>
       </c>
       <c r="C33" s="12" t="s">
@@ -4433,7 +4441,7 @@
       </c>
     </row>
     <row r="34" spans="2:18" ht="27.75">
-      <c r="B34" s="108" t="s">
+      <c r="B34" s="101" t="s">
         <v>114</v>
       </c>
       <c r="C34" s="12" t="s">
@@ -4474,7 +4482,7 @@
       </c>
     </row>
     <row r="35" spans="2:18">
-      <c r="B35" s="108" t="s">
+      <c r="B35" s="101" t="s">
         <v>195</v>
       </c>
       <c r="C35" s="12" t="s">
@@ -4527,7 +4535,7 @@
       </c>
     </row>
     <row r="36" spans="2:18" ht="41.65">
-      <c r="B36" s="108" t="s">
+      <c r="B36" s="101" t="s">
         <v>113</v>
       </c>
       <c r="C36" s="12" t="s">
@@ -4580,7 +4588,7 @@
       </c>
     </row>
     <row r="37" spans="2:18">
-      <c r="B37" s="108" t="s">
+      <c r="B37" s="101" t="s">
         <v>112</v>
       </c>
       <c r="C37" s="6" t="s">
@@ -4633,7 +4641,7 @@
       </c>
     </row>
     <row r="38" spans="2:18" ht="41.65">
-      <c r="B38" s="108" t="s">
+      <c r="B38" s="101" t="s">
         <v>111</v>
       </c>
       <c r="C38" s="12" t="s">
@@ -4686,7 +4694,7 @@
       </c>
     </row>
     <row r="39" spans="2:18">
-      <c r="B39" s="108" t="s">
+      <c r="B39" s="101" t="s">
         <v>110</v>
       </c>
       <c r="C39" s="6" t="s">
@@ -4739,7 +4747,7 @@
       </c>
     </row>
     <row r="40" spans="2:18">
-      <c r="B40" s="108" t="s">
+      <c r="B40" s="101" t="s">
         <v>109</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -4792,7 +4800,7 @@
       </c>
     </row>
     <row r="41" spans="2:18">
-      <c r="B41" s="108" t="s">
+      <c r="B41" s="101" t="s">
         <v>108</v>
       </c>
       <c r="C41" s="6" t="s">
@@ -4845,7 +4853,7 @@
       </c>
     </row>
     <row r="42" spans="2:18">
-      <c r="B42" s="108" t="s">
+      <c r="B42" s="101" t="s">
         <v>107</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -4898,7 +4906,7 @@
       </c>
     </row>
     <row r="43" spans="2:18">
-      <c r="B43" s="109" t="s">
+      <c r="B43" s="102" t="s">
         <v>106</v>
       </c>
       <c r="C43" s="7" t="s">
@@ -4951,7 +4959,7 @@
       </c>
     </row>
     <row r="44" spans="2:18" ht="14.65" thickBot="1">
-      <c r="B44" s="110" t="s">
+      <c r="B44" s="103" t="s">
         <v>196</v>
       </c>
       <c r="C44" s="18" t="s">
@@ -5630,7 +5638,7 @@
       </c>
     </row>
     <row r="61" spans="2:18" ht="28.5">
-      <c r="B61" s="100" t="s">
+      <c r="B61" s="93" t="s">
         <v>91</v>
       </c>
       <c r="C61" s="12" t="s">
@@ -5673,7 +5681,7 @@
       </c>
     </row>
     <row r="62" spans="2:18" ht="28.5">
-      <c r="B62" s="101" t="s">
+      <c r="B62" s="94" t="s">
         <v>90</v>
       </c>
       <c r="C62" s="12" t="s">
@@ -5716,7 +5724,7 @@
       </c>
     </row>
     <row r="63" spans="2:18" ht="28.5">
-      <c r="B63" s="101" t="s">
+      <c r="B63" s="94" t="s">
         <v>89</v>
       </c>
       <c r="C63" s="12" t="s">
@@ -5759,7 +5767,7 @@
       </c>
     </row>
     <row r="64" spans="2:18" ht="28.5">
-      <c r="B64" s="101" t="s">
+      <c r="B64" s="94" t="s">
         <v>88</v>
       </c>
       <c r="C64" s="12" t="s">
@@ -5802,7 +5810,7 @@
       </c>
     </row>
     <row r="65" spans="2:18" ht="28.5">
-      <c r="B65" s="101" t="s">
+      <c r="B65" s="94" t="s">
         <v>87</v>
       </c>
       <c r="C65" s="12" t="s">
@@ -5845,7 +5853,7 @@
       </c>
     </row>
     <row r="66" spans="2:18" ht="28.5">
-      <c r="B66" s="101" t="s">
+      <c r="B66" s="94" t="s">
         <v>86</v>
       </c>
       <c r="C66" s="12" t="s">
@@ -5888,7 +5896,7 @@
       </c>
     </row>
     <row r="67" spans="2:18" ht="28.5">
-      <c r="B67" s="101" t="s">
+      <c r="B67" s="94" t="s">
         <v>85</v>
       </c>
       <c r="C67" s="12" t="s">
@@ -5931,7 +5939,7 @@
       </c>
     </row>
     <row r="68" spans="2:18">
-      <c r="B68" s="101" t="s">
+      <c r="B68" s="94" t="s">
         <v>84</v>
       </c>
       <c r="C68" s="6" t="s">
@@ -5974,7 +5982,7 @@
       </c>
     </row>
     <row r="69" spans="2:18">
-      <c r="B69" s="101" t="s">
+      <c r="B69" s="94" t="s">
         <v>83</v>
       </c>
       <c r="C69" s="6" t="s">
@@ -6017,7 +6025,7 @@
       </c>
     </row>
     <row r="70" spans="2:18">
-      <c r="B70" s="101" t="s">
+      <c r="B70" s="94" t="s">
         <v>82</v>
       </c>
       <c r="C70" s="6" t="s">
@@ -6060,7 +6068,7 @@
       </c>
     </row>
     <row r="71" spans="2:18">
-      <c r="B71" s="101" t="s">
+      <c r="B71" s="94" t="s">
         <v>81</v>
       </c>
       <c r="C71" s="6" t="s">
@@ -6103,7 +6111,7 @@
       </c>
     </row>
     <row r="72" spans="2:18">
-      <c r="B72" s="101" t="s">
+      <c r="B72" s="94" t="s">
         <v>80</v>
       </c>
       <c r="C72" s="6" t="s">
@@ -6146,7 +6154,7 @@
       </c>
     </row>
     <row r="73" spans="2:18">
-      <c r="B73" s="101" t="s">
+      <c r="B73" s="94" t="s">
         <v>79</v>
       </c>
       <c r="C73" s="6" t="s">
@@ -6189,7 +6197,7 @@
       </c>
     </row>
     <row r="74" spans="2:18">
-      <c r="B74" s="101" t="s">
+      <c r="B74" s="94" t="s">
         <v>78</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -6232,7 +6240,7 @@
       </c>
     </row>
     <row r="75" spans="2:18">
-      <c r="B75" s="101" t="s">
+      <c r="B75" s="94" t="s">
         <v>77</v>
       </c>
       <c r="C75" s="6" t="s">
@@ -6275,7 +6283,7 @@
       </c>
     </row>
     <row r="76" spans="2:18">
-      <c r="B76" s="101" t="s">
+      <c r="B76" s="94" t="s">
         <v>76</v>
       </c>
       <c r="C76" s="6" t="s">
@@ -6318,7 +6326,7 @@
       </c>
     </row>
     <row r="77" spans="2:18">
-      <c r="B77" s="101" t="s">
+      <c r="B77" s="94" t="s">
         <v>75</v>
       </c>
       <c r="C77" s="6" t="s">
@@ -6361,7 +6369,7 @@
       </c>
     </row>
     <row r="78" spans="2:18">
-      <c r="B78" s="101" t="s">
+      <c r="B78" s="94" t="s">
         <v>74</v>
       </c>
       <c r="C78" s="6" t="s">
@@ -6404,7 +6412,7 @@
       </c>
     </row>
     <row r="79" spans="2:18">
-      <c r="B79" s="101" t="s">
+      <c r="B79" s="94" t="s">
         <v>73</v>
       </c>
       <c r="C79" s="6" t="s">
@@ -6447,7 +6455,7 @@
       </c>
     </row>
     <row r="80" spans="2:18">
-      <c r="B80" s="101" t="s">
+      <c r="B80" s="94" t="s">
         <v>72</v>
       </c>
       <c r="C80" s="6" t="s">
@@ -6490,7 +6498,7 @@
       </c>
     </row>
     <row r="81" spans="2:18">
-      <c r="B81" s="101" t="s">
+      <c r="B81" s="94" t="s">
         <v>71</v>
       </c>
       <c r="C81" s="6" t="s">
@@ -6533,7 +6541,7 @@
       </c>
     </row>
     <row r="82" spans="2:18">
-      <c r="B82" s="101" t="s">
+      <c r="B82" s="94" t="s">
         <v>70</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -6576,7 +6584,7 @@
       </c>
     </row>
     <row r="83" spans="2:18">
-      <c r="B83" s="101" t="s">
+      <c r="B83" s="94" t="s">
         <v>69</v>
       </c>
       <c r="C83" s="6" t="s">
@@ -6619,7 +6627,7 @@
       </c>
     </row>
     <row r="84" spans="2:18">
-      <c r="B84" s="101" t="s">
+      <c r="B84" s="94" t="s">
         <v>68</v>
       </c>
       <c r="C84" s="6" t="s">
@@ -6662,7 +6670,7 @@
       </c>
     </row>
     <row r="85" spans="2:18" ht="28.5">
-      <c r="B85" s="101" t="s">
+      <c r="B85" s="94" t="s">
         <v>67</v>
       </c>
       <c r="C85" s="6" t="s">
@@ -6705,7 +6713,7 @@
       </c>
     </row>
     <row r="86" spans="2:18" ht="28.5">
-      <c r="B86" s="101" t="s">
+      <c r="B86" s="94" t="s">
         <v>66</v>
       </c>
       <c r="C86" s="6" t="s">
@@ -6748,7 +6756,7 @@
       </c>
     </row>
     <row r="87" spans="2:18" ht="28.5">
-      <c r="B87" s="102" t="s">
+      <c r="B87" s="95" t="s">
         <v>65</v>
       </c>
       <c r="C87" s="6" t="s">
@@ -6791,7 +6799,7 @@
       </c>
     </row>
     <row r="88" spans="2:18">
-      <c r="B88" s="101" t="s">
+      <c r="B88" s="94" t="s">
         <v>64</v>
       </c>
       <c r="C88" s="15" t="s">
@@ -6834,7 +6842,7 @@
       </c>
     </row>
     <row r="89" spans="2:18">
-      <c r="B89" s="101" t="s">
+      <c r="B89" s="94" t="s">
         <v>63</v>
       </c>
       <c r="C89" s="6" t="s">
@@ -6877,7 +6885,7 @@
       </c>
     </row>
     <row r="90" spans="2:18">
-      <c r="B90" s="102" t="s">
+      <c r="B90" s="95" t="s">
         <v>62</v>
       </c>
       <c r="C90" s="13" t="s">
@@ -6920,7 +6928,7 @@
       </c>
     </row>
     <row r="91" spans="2:18">
-      <c r="B91" s="102" t="s">
+      <c r="B91" s="95" t="s">
         <v>61</v>
       </c>
       <c r="C91" s="13" t="s">
@@ -6963,7 +6971,7 @@
       </c>
     </row>
     <row r="92" spans="2:18">
-      <c r="B92" s="102" t="s">
+      <c r="B92" s="95" t="s">
         <v>60</v>
       </c>
       <c r="C92" s="13" t="s">
@@ -7006,7 +7014,7 @@
       </c>
     </row>
     <row r="93" spans="2:18">
-      <c r="B93" s="102" t="s">
+      <c r="B93" s="95" t="s">
         <v>59</v>
       </c>
       <c r="C93" s="13" t="s">
@@ -7049,7 +7057,7 @@
       </c>
     </row>
     <row r="94" spans="2:18">
-      <c r="B94" s="102" t="s">
+      <c r="B94" s="95" t="s">
         <v>58</v>
       </c>
       <c r="C94" s="13" t="s">
@@ -7092,7 +7100,7 @@
       </c>
     </row>
     <row r="95" spans="2:18">
-      <c r="B95" s="102" t="s">
+      <c r="B95" s="95" t="s">
         <v>209</v>
       </c>
       <c r="C95" s="13" t="s">
@@ -7135,7 +7143,7 @@
       </c>
     </row>
     <row r="96" spans="2:18">
-      <c r="B96" s="102" t="s">
+      <c r="B96" s="95" t="s">
         <v>56</v>
       </c>
       <c r="C96" s="17" t="s">
@@ -7178,7 +7186,7 @@
       </c>
     </row>
     <row r="97" spans="2:18" ht="14.65" thickBot="1">
-      <c r="B97" s="103" t="s">
+      <c r="B97" s="96" t="s">
         <v>55</v>
       </c>
       <c r="C97" s="18" t="s">
@@ -7275,7 +7283,7 @@
       </c>
     </row>
     <row r="100" spans="2:18" ht="42.75">
-      <c r="B100" s="104" t="s">
+      <c r="B100" s="97" t="s">
         <v>53</v>
       </c>
       <c r="C100" s="12" t="s">
@@ -7318,7 +7326,7 @@
       </c>
     </row>
     <row r="101" spans="2:18">
-      <c r="B101" s="105" t="s">
+      <c r="B101" s="98" t="s">
         <v>52</v>
       </c>
       <c r="C101" s="6" t="s">
@@ -7361,7 +7369,7 @@
       </c>
     </row>
     <row r="102" spans="2:18" ht="42.75">
-      <c r="B102" s="105" t="s">
+      <c r="B102" s="98" t="s">
         <v>51</v>
       </c>
       <c r="C102" s="12" t="s">
@@ -7404,7 +7412,7 @@
       </c>
     </row>
     <row r="103" spans="2:18" ht="42.75">
-      <c r="B103" s="105" t="s">
+      <c r="B103" s="98" t="s">
         <v>50</v>
       </c>
       <c r="C103" s="12" t="s">
@@ -7447,7 +7455,7 @@
       </c>
     </row>
     <row r="104" spans="2:18">
-      <c r="B104" s="105" t="s">
+      <c r="B104" s="98" t="s">
         <v>49</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -7490,7 +7498,7 @@
       </c>
     </row>
     <row r="105" spans="2:18" ht="42.75">
-      <c r="B105" s="105" t="s">
+      <c r="B105" s="98" t="s">
         <v>48</v>
       </c>
       <c r="C105" s="6" t="s">
@@ -7533,7 +7541,7 @@
       </c>
     </row>
     <row r="106" spans="2:18" ht="43.15" thickBot="1">
-      <c r="B106" s="106" t="s">
+      <c r="B106" s="99" t="s">
         <v>47</v>
       </c>
       <c r="C106" s="18" t="s">
@@ -8304,7 +8312,7 @@
       </c>
     </row>
     <row r="124" spans="2:20" ht="42.75">
-      <c r="B124" s="93" t="s">
+      <c r="B124" s="105" t="s">
         <v>24</v>
       </c>
       <c r="C124" s="6" t="s">
@@ -8347,7 +8355,7 @@
       </c>
     </row>
     <row r="125" spans="2:20" ht="28.5">
-      <c r="B125" s="93" t="s">
+      <c r="B125" s="105" t="s">
         <v>23</v>
       </c>
       <c r="C125" s="6" t="s">
@@ -8390,7 +8398,7 @@
       </c>
     </row>
     <row r="126" spans="2:20" ht="28.5">
-      <c r="B126" s="93" t="s">
+      <c r="B126" s="105" t="s">
         <v>18</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -8433,7 +8441,7 @@
       </c>
     </row>
     <row r="127" spans="2:20">
-      <c r="B127" s="93" t="s">
+      <c r="B127" s="105" t="s">
         <v>17</v>
       </c>
       <c r="C127" s="6" t="s">
@@ -8476,7 +8484,7 @@
       </c>
     </row>
     <row r="128" spans="2:20">
-      <c r="B128" s="93" t="s">
+      <c r="B128" s="105" t="s">
         <v>16</v>
       </c>
       <c r="C128" s="6" t="s">
@@ -8509,7 +8517,7 @@
       </c>
     </row>
     <row r="129" spans="2:18">
-      <c r="B129" s="93" t="s">
+      <c r="B129" s="105" t="s">
         <v>15</v>
       </c>
       <c r="C129" s="6" t="s">
@@ -8552,7 +8560,7 @@
       </c>
     </row>
     <row r="130" spans="2:18">
-      <c r="B130" s="93" t="s">
+      <c r="B130" s="105" t="s">
         <v>14</v>
       </c>
       <c r="C130" s="6" t="s">
@@ -8595,7 +8603,7 @@
       </c>
     </row>
     <row r="131" spans="2:18">
-      <c r="B131" s="93" t="s">
+      <c r="B131" s="105" t="s">
         <v>10</v>
       </c>
       <c r="C131" s="6" t="s">
@@ -8648,7 +8656,7 @@
       </c>
     </row>
     <row r="132" spans="2:18">
-      <c r="B132" s="93" t="s">
+      <c r="B132" s="105" t="s">
         <v>9</v>
       </c>
       <c r="C132" s="6" t="s">
@@ -8701,7 +8709,7 @@
       </c>
     </row>
     <row r="133" spans="2:18">
-      <c r="B133" s="93" t="s">
+      <c r="B133" s="105" t="s">
         <v>8</v>
       </c>
       <c r="C133" s="6" t="s">
@@ -8754,7 +8762,7 @@
       </c>
     </row>
     <row r="134" spans="2:18">
-      <c r="B134" s="94" t="s">
+      <c r="B134" s="106" t="s">
         <v>183</v>
       </c>
       <c r="C134" s="13" t="s">
@@ -8807,7 +8815,7 @@
       </c>
     </row>
     <row r="135" spans="2:18">
-      <c r="B135" s="95" t="s">
+      <c r="B135" s="107" t="s">
         <v>7</v>
       </c>
       <c r="C135" s="7" t="s">
@@ -8850,7 +8858,7 @@
       </c>
     </row>
     <row r="136" spans="2:18">
-      <c r="B136" s="96" t="s">
+      <c r="B136" s="108" t="s">
         <v>5</v>
       </c>
       <c r="C136" s="16" t="s">
@@ -8893,7 +8901,7 @@
       </c>
     </row>
     <row r="137" spans="2:18">
-      <c r="B137" s="97" t="s">
+      <c r="B137" s="109" t="s">
         <v>185</v>
       </c>
       <c r="C137" s="28" t="s">
@@ -8946,7 +8954,7 @@
       </c>
     </row>
     <row r="138" spans="2:18">
-      <c r="B138" s="97" t="s">
+      <c r="B138" s="109" t="s">
         <v>187</v>
       </c>
       <c r="C138" s="28" t="s">
@@ -8999,7 +9007,7 @@
       </c>
     </row>
     <row r="139" spans="2:18">
-      <c r="B139" s="97" t="s">
+      <c r="B139" s="109" t="s">
         <v>4</v>
       </c>
       <c r="C139" s="14" t="s">
@@ -9032,7 +9040,7 @@
       </c>
     </row>
     <row r="140" spans="2:18">
-      <c r="B140" s="98" t="s">
+      <c r="B140" s="110" t="s">
         <v>2</v>
       </c>
       <c r="C140" s="14" t="s">
@@ -9085,7 +9093,7 @@
       </c>
     </row>
     <row r="141" spans="2:18">
-      <c r="B141" s="96" t="s">
+      <c r="B141" s="108" t="s">
         <v>190</v>
       </c>
       <c r="C141" s="14" t="s">
@@ -9138,7 +9146,7 @@
       </c>
     </row>
     <row r="142" spans="2:18" ht="14.65" thickBot="1">
-      <c r="B142" s="99" t="s">
+      <c r="B142" s="111" t="s">
         <v>1</v>
       </c>
       <c r="C142" s="9" t="s">
@@ -9191,29 +9199,15 @@
       </c>
     </row>
     <row r="143" spans="2:18" ht="14.65" thickTop="1"/>
+    <row r="150" spans="3:3">
+      <c r="C150" s="104"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F24FF01B6E691B418AC7A3AA007394EC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2842777d906afb735552f47e63b23c65">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8f43ef-8ea4-412d-9c18-5388ad596486" xmlns:ns4="c1e77170-3c0a-491c-a033-5a7c184eabd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="352f9ab862d979d0253968f43d118292" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
@@ -9432,32 +9426,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53964A40-A6D0-45D9-B1D4-1342A31D1BCB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35331C5A-856A-46E2-8755-4FFF5881D9DA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9474,4 +9460,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53964A40-A6D0-45D9-B1D4-1342A31D1BCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data-source/技能数据.xlsx
+++ b/data-source/技能数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9D8BAE-8467-47FB-B785-6FE210316FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE28897-4E7C-467B-A300-731F754B0B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F03E0F5E-A49D-457A-ADAE-8FAE4055FE2C}"/>
   </bookViews>
@@ -41,9 +41,474 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="282">
   <si>
-    <r>
-      <t>被攻击时有</t>
-    </r>
+    <t>格挡大师</t>
+  </si>
+  <si>
+    <t>熟练的召唤师</t>
+  </si>
+  <si>
+    <t>对敌人每次连续攻击伤害+2，攻击速度+5%</t>
+  </si>
+  <si>
+    <t>战斗狂怒</t>
+  </si>
+  <si>
+    <t>快速重载</t>
+  </si>
+  <si>
+    <r>
+      <t>放置符文的速度快</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5%</t>
+    </r>
+  </si>
+  <si>
+    <t>符文操控者</t>
+  </si>
+  <si>
+    <t>猎人</t>
+  </si>
+  <si>
+    <t>训练有素的猫咪</t>
+  </si>
+  <si>
+    <t>训练过的狼</t>
+  </si>
+  <si>
+    <t>凝固的血液</t>
+  </si>
+  <si>
+    <t>防霜</t>
+  </si>
+  <si>
+    <t>防火</t>
+  </si>
+  <si>
+    <t>设陷阱者</t>
+  </si>
+  <si>
+    <t>精力充沛</t>
+  </si>
+  <si>
+    <t>超级专注</t>
+  </si>
+  <si>
+    <t>重生</t>
+  </si>
+  <si>
+    <t>群防</t>
+  </si>
+  <si>
+    <t>无畏</t>
+  </si>
+  <si>
+    <t>势不可挡</t>
+  </si>
+  <si>
+    <t>免疫</t>
+  </si>
+  <si>
+    <t>铁胃</t>
+  </si>
+  <si>
+    <t>护火者</t>
+  </si>
+  <si>
+    <t>探路人</t>
+  </si>
+  <si>
+    <t>治疗休息</t>
+  </si>
+  <si>
+    <t>Lvl 15</t>
+  </si>
+  <si>
+    <t>Lvl 14</t>
+  </si>
+  <si>
+    <t>Lvl 13</t>
+  </si>
+  <si>
+    <t>Lvl 12</t>
+  </si>
+  <si>
+    <t>Lvl 11</t>
+  </si>
+  <si>
+    <t>Lvl 10</t>
+  </si>
+  <si>
+    <t>Lvl 9</t>
+  </si>
+  <si>
+    <t>Lvl 8</t>
+  </si>
+  <si>
+    <t>Lvl 7</t>
+  </si>
+  <si>
+    <t>Lvl 6</t>
+  </si>
+  <si>
+    <t>Lvl 5</t>
+  </si>
+  <si>
+    <t>Lvl 4</t>
+  </si>
+  <si>
+    <t>Lvl 3</t>
+  </si>
+  <si>
+    <t>Lvl 2</t>
+  </si>
+  <si>
+    <t>Lvl 1</t>
+  </si>
+  <si>
+    <t>特殊</t>
+  </si>
+  <si>
+    <t>食物强化</t>
+  </si>
+  <si>
+    <t>饮料强化</t>
+  </si>
+  <si>
+    <t>强力生命值</t>
+  </si>
+  <si>
+    <t>奔跑速度</t>
+  </si>
+  <si>
+    <t>角色</t>
+  </si>
+  <si>
+    <t>浆果</t>
+  </si>
+  <si>
+    <t>亚麻纤维</t>
+  </si>
+  <si>
+    <t>铁矿石</t>
+  </si>
+  <si>
+    <t>铜矿石</t>
+  </si>
+  <si>
+    <t>石灰岩</t>
+  </si>
+  <si>
+    <t>原桦木</t>
+  </si>
+  <si>
+    <t>原松木</t>
+  </si>
+  <si>
+    <t>资源</t>
+  </si>
+  <si>
+    <t>哈特碎片</t>
+  </si>
+  <si>
+    <t>哈利德祭祀</t>
+  </si>
+  <si>
+    <t>1%闪避概率</t>
+  </si>
+  <si>
+    <t>恐怖蝙蝠</t>
+  </si>
+  <si>
+    <t>骷髅</t>
+  </si>
+  <si>
+    <t>哀悼死神的影子</t>
+  </si>
+  <si>
+    <t>大车炮台中尉</t>
+  </si>
+  <si>
+    <t>大车炮台士兵</t>
+  </si>
+  <si>
+    <t>抄写员幽灵</t>
+  </si>
+  <si>
+    <t>科学家幽灵</t>
+  </si>
+  <si>
+    <t>被咒狂徒</t>
+  </si>
+  <si>
+    <t>被咒勇士</t>
+  </si>
+  <si>
+    <t>瘟疫缠身者</t>
+  </si>
+  <si>
+    <t>火焰守卫</t>
+  </si>
+  <si>
+    <t>残忍酷吏</t>
+  </si>
+  <si>
+    <t>惩罚者</t>
+  </si>
+  <si>
+    <t>猎头者</t>
+  </si>
+  <si>
+    <t>酷吏</t>
+  </si>
+  <si>
+    <t>女祭司</t>
+  </si>
+  <si>
+    <t>掷斧者</t>
+  </si>
+  <si>
+    <t>屠宰者</t>
+  </si>
+  <si>
+    <t>痛苦者</t>
+  </si>
+  <si>
+    <t>亵渎者</t>
+  </si>
+  <si>
+    <t>被弃者</t>
+  </si>
+  <si>
+    <t>被附身者</t>
+  </si>
+  <si>
+    <t>瘟疫之卵</t>
+  </si>
+  <si>
+    <t>麻风战士</t>
+  </si>
+  <si>
+    <t>瘟疫野蛮人</t>
+  </si>
+  <si>
+    <t>瘟疫强盗</t>
+  </si>
+  <si>
+    <t>黑暗猎人</t>
+  </si>
+  <si>
+    <t>被咒圣殿骑士</t>
+  </si>
+  <si>
+    <t>被咒骑士</t>
+  </si>
+  <si>
+    <t>恐狼</t>
+  </si>
+  <si>
+    <t>被咒者</t>
+  </si>
+  <si>
+    <t>熊</t>
+  </si>
+  <si>
+    <t>狼</t>
+  </si>
+  <si>
+    <t>麻风病人</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>曼德拉药酒</t>
+  </si>
+  <si>
+    <t>苦药酒</t>
+  </si>
+  <si>
+    <t>香料酒</t>
+  </si>
+  <si>
+    <t>蘑菇浸剂</t>
+  </si>
+  <si>
+    <t>蜂蜜桶</t>
+  </si>
+  <si>
+    <t>麦芽酒</t>
+  </si>
+  <si>
+    <t>绷带</t>
+  </si>
+  <si>
+    <t>牛肉干</t>
+  </si>
+  <si>
+    <t>韭葱汤</t>
+  </si>
+  <si>
+    <t>浆果饮料</t>
+  </si>
+  <si>
+    <t>烤肉</t>
+  </si>
+  <si>
+    <t>烤韭葱</t>
+  </si>
+  <si>
+    <t>治疗</t>
+  </si>
+  <si>
+    <t>弓与弩</t>
+  </si>
+  <si>
+    <t>护盾</t>
+  </si>
+  <si>
+    <t>戟</t>
+  </si>
+  <si>
+    <t>长剑</t>
+  </si>
+  <si>
+    <t>双刃大砍刀</t>
+  </si>
+  <si>
+    <t>短弯刀</t>
+  </si>
+  <si>
+    <t>战争刀</t>
+  </si>
+  <si>
+    <t>变种剑</t>
+  </si>
+  <si>
+    <t>弯刀</t>
+  </si>
+  <si>
+    <t>法兰锤</t>
+  </si>
+  <si>
+    <t>铜战斧</t>
+  </si>
+  <si>
+    <t>流星锤</t>
+  </si>
+  <si>
+    <t>尖刺锤</t>
+  </si>
+  <si>
+    <t>单手剑</t>
+  </si>
+  <si>
+    <t>浆</t>
+  </si>
+  <si>
+    <t>长柄叉</t>
+  </si>
+  <si>
+    <t>匕首</t>
+  </si>
+  <si>
+    <t>锹</t>
+  </si>
+  <si>
+    <t>铁匠锤</t>
+  </si>
+  <si>
+    <t>车把</t>
+  </si>
+  <si>
+    <t>镰刀</t>
+  </si>
+  <si>
+    <t>火把</t>
+  </si>
+  <si>
+    <t>锄头</t>
+  </si>
+  <si>
+    <t>棍子</t>
+  </si>
+  <si>
+    <t>拳头</t>
+  </si>
+  <si>
+    <t>伤害</t>
+  </si>
+  <si>
+    <t>杀死司令</t>
+  </si>
+  <si>
+    <t>诅咒</t>
+  </si>
+  <si>
+    <t>抑制</t>
+  </si>
+  <si>
+    <t>石化</t>
+  </si>
+  <si>
+    <t>防御姿态</t>
+  </si>
+  <si>
+    <t>惩罚</t>
+  </si>
+  <si>
+    <t>循环效应</t>
+  </si>
+  <si>
+    <t>眩晕一击</t>
+  </si>
+  <si>
+    <t>重击</t>
+  </si>
+  <si>
+    <t>吓跑夜游神，升级可以提高充能速度</t>
+  </si>
+  <si>
+    <t>黑暗驱逐者</t>
+  </si>
+  <si>
+    <t>渡鸦之眼</t>
+  </si>
+  <si>
+    <t>疾跑</t>
+  </si>
+  <si>
+    <t>主动技能</t>
+  </si>
+  <si>
+    <t>抗衰败</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>% 闪避概率</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -59,27 +524,1052 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>的几率给护盾瞬间充能（1-4级在破损大车/堕落骑士）</t>
-    </r>
-  </si>
-  <si>
-    <t>格挡大师</t>
-  </si>
-  <si>
-    <t>熟练的召唤师</t>
-  </si>
-  <si>
-    <t>对敌人每次连续攻击伤害+2，攻击速度+5%</t>
-  </si>
-  <si>
-    <t>战斗狂怒</t>
-  </si>
-  <si>
-    <t>快速重载</t>
-  </si>
-  <si>
-    <r>
-      <t>放置符文的速度快</t>
+      <t>闪避概率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">治疗提高 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>伤害加</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>% 几率获取额外资源</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>% 几率获取额外资源</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>地点奔跑速度提高</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">最大生命值提高 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>在家里每呆上10秒，就能恢复</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>点生命值</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">饱食度最大值增加 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">饮料条最大值增加 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">将毒素伤害减少 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">减少出血造成的伤害 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>减少火焰伤害</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">将地点之间的步行时间减少 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>火把燃烧时间延长</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">% </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>食物和饮料中毒抗性为</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>受到致命一击后重生概率为</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>能量回复速度增加</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>被困时，敌人收到伤害增加</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">你的恶狼造成的伤害增加 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>放置陷阱的速度快了</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>你重新装弩的速度快了</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>将地点奔跑速度提高</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>，持续5秒</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>进行鸟瞰，可以将视野范围提高</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>200%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>你的下次攻击造成</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>点额外伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>下次攻击可使敌人击晕</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>0.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>秒</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>对方圆3米内的敌人造成</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>点纯伤害</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>反弹敌人给予的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>14%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>物理伤害，持续3秒</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>护甲提高</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>14%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>，持续5秒</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>变成石头，持续</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>秒，期间获得无敌效果并且持续治疗</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>下次攻击将减慢敌人攻击速度</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>，持续7秒</t>
+    </r>
+  </si>
+  <si>
+    <t>下次攻击会让敌人变得虚弱，收到的物理伤害增加8%，持续7秒</t>
+  </si>
+  <si>
+    <r>
+      <t>暂时提高恐狼移速60%，攻速40%，以及伤害</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>，持续7秒</t>
+    </r>
+  </si>
+  <si>
+    <t>精打细算的猎人</t>
+  </si>
+  <si>
+    <t>用工兵套件拆除陷阱后，有25%的几率将其拾起</t>
+  </si>
+  <si>
+    <t>灵巧弩手</t>
+  </si>
+  <si>
+    <t>击败目标后，有10%的几率立即装填弩</t>
+  </si>
+  <si>
+    <t>猎人之眼</t>
+  </si>
+  <si>
+    <t>使用远程武器时，视野增加50%</t>
+  </si>
+  <si>
+    <t>如果附近有一个以上的敌人，护甲提高5</t>
+  </si>
+  <si>
+    <t>熟练的珠宝匠</t>
+  </si>
+  <si>
+    <t>激活时有1%的几率保留护符的奶就度</t>
+  </si>
+  <si>
+    <r>
+      <t>减少寒冷伤害</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>减少衰败造成的伤害</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%</t>
+    </r>
+  </si>
+  <si>
+    <t>青铜矛</t>
+  </si>
+  <si>
+    <t>狂战士战斧</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">所有护盾耐用度增加 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>一次发射两支箭的概率为</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%</t>
+    </r>
+  </si>
+  <si>
+    <t>冰环</t>
+  </si>
+  <si>
+    <t>短暂冻结附近敌人，目标数量：1</t>
+  </si>
+  <si>
+    <t>治疗提高 2</t>
+  </si>
+  <si>
+    <t>治疗提高2</t>
+  </si>
+  <si>
+    <t>掉落地点</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10: 古人墓穴；</t>
+  </si>
+  <si>
+    <t>增加召唤生物的生命值5%</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：哈利德；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：哈特；</t>
+  </si>
+  <si>
+    <t>弗拉格纳的侍女</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：弗拉格纳；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：大车炮台；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10: 古人墓穴/大车炮台；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：西方银矿/继母艾莎；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：继母艾莎；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：西方银矿；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10: 古人墓穴/西方银矿；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：看守者棚屋；Lv1-Lv10：大车炮台；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv4：看守者棚屋；Lv1-Lv10：大车炮台；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：游商</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：游商/酷吏地下城</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：酷吏地下城；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：酷吏地下城；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：被诅咒的天文台</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：叛徒地下墓穴；Lv1-Lv10: 古人墓穴/酷吏地下城；Lv5-Lv10：大车炮台；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：叛徒地下墓穴；Lv5-Lv10：大车炮台；Lv1-Lv10：酷吏地下城</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：酷吏地下城；Lv1-Lv8：叛徒地下墓穴</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：城堡</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：大车炮台/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：4级图；Lv5-Lv10：5级图；Lv1-Lv10：城堡</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：4级图；Lv1-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：4级图；Lv1-Lv7：5级图/城堡；Lv6-Lv10：酷吏地下城；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：酷吏地下城；Lv1-Lv6：被诅咒的天文台</t>
+  </si>
+  <si>
+    <t>Lv1-Lv4：4级图；Lv1-Lv8：5级图/城堡；Lv5-Lv10：大车炮台；Lv6-Lv10：酷吏地下城</t>
+  </si>
+  <si>
+    <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士</t>
+  </si>
+  <si>
+    <t>Lv1-Lv6：叛徒地下墓穴；Lv7-Lv8：商人护送；Lv1-Lv8：酷吏地下城</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：死灵法师的巢穴；Lv1-Lv10: 古人墓穴/西方银矿/被诅咒的天文台；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：死灵法师的巢穴；Lv1-Lv10：西方银矿/继母艾莎；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv4：1-3级图/墓地之夜；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv8：哈特/弗拉格纳；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：继母艾莎</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：死灵法师的巢穴；Lv1-Lv10: 古人墓穴/西方银矿/继母艾莎；</t>
+  </si>
+  <si>
+    <t>Lv5-Lv10：大车炮台；Lv1-Lv9：继母艾莎；Lv6-Lv10：酷吏地下城</t>
+  </si>
+  <si>
+    <t>待测</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%闪避概率</t>
+    </r>
+  </si>
+  <si>
+    <t>Lv1：哈利德/哈特/弗拉格纳/1-3级图/地下神祠/墓地之夜/小型被弃者地窖/被弃者地窖；Lv1-Lv2：4级图/5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：哈利德/哈特/弗拉格纳/1-3级图/地下神祠/墓地之夜/小型被弃者地窖/被弃者地窖；Lv2-Lv3：4级图/5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：地下神祠/墓地之夜/小型被弃者地窖；Lv1-Lv3：哈利德/哈特/弗拉格纳/1-3级图/被弃者地窖；Lv3-Lv4：4级图/5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：地下神祠/墓地之夜/小型被弃者地窖；Lv1-Lv4：哈利德/哈特/弗拉格纳/1-3级图/被弃者地窖；Lv4-Lv5：4级图/5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：1-3级图/小型被弃者地窖/被弃者地窖；Lv1-Lv4：墓地之夜；Lv4-Lv7：被弃者地下城/大型被弃者地窖；Lv5-Lv7：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：1-3级图/小型被弃者地窖/被弃者地窖；Lv1-Lv4：墓地之夜；Lv5-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；Lv1-Lv10：被诅咒的天文台</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；Lv1-Lv10：大车炮台；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv7-Lv8：商人护送；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv8：4级图；Lv5-Lv10：5级图/城堡；Lv1-Lv10：大车炮台；</t>
+  </si>
+  <si>
+    <t>Lv1：野蛮人营地；Lv1-Lv10: 古人墓穴/被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv10：被弃者地下城/大型被弃者地窖；Lv3-Lv5：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv6：4级图；Lv5-Lv8：5级图/城堡；Lv1-Lv10：被诅咒的天文台</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：1-3级图/小型被弃者地窖/被弃者地窖；Lv1-Lv4：墓地之夜；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：大车炮台/被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士；Lv1-Lv10：被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：被弃者地下城/地下神祠/堕落骑士/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/铜矿/墓地之夜/被弃者地窖；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv8：小型被弃者地窖；Lv1-Lv10：被弃者地窖/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv8：小型被弃者地窖；Lv1-Lv10：继母艾莎/被弃者地窖/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv8：小型被弃者地窖/被弃者地窖；Lv1-Lv10：继母艾莎/大型被弃者地窖</t>
+  </si>
+  <si>
+    <t>Lv1-Lv4：被弃者地窖；Lv1-Lv10：继母艾莎/大型被弃者地窖</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv10：被弃者地下城/大型被弃者地窖；Lv3-Lv6：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv7：4级图；Lv5-Lv8：5级图/城堡；Lv1-Lv10：大车炮台；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；Lv1-Lv10：大车炮台；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv5：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv6：4级图；Lv3-Lv10：被弃者地下城；Lv5-Lv8：城堡；Lv3-Lv10：大型被弃者地窖</t>
+  </si>
+  <si>
+    <t>Lv1-Lv10：大车炮台被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士；Lv1-Lv10: 古人墓穴/大车炮台/被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：哈利德/哈特/弗拉格纳/被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：哈利德/哈特/弗拉格纳/被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；Lv1-Lv10：被诅咒的天文台</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv4-Lv5：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv5：被弃者地下城/地下神祠/大型被弃者地窖；Lv1-Lv6：哈利德/哈特/弗拉格纳；Lv5-Lv6：4级图/5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv5-Lv7：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv5-Lv8：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv1-Lv9：被弃者地下城/大型被弃者地窖；Lv5-Lv8：5级图/城堡；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：叛徒地下墓穴/继母艾莎；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv5-Lv10：大车炮台/酷吏地下城；Lv5-Lv8：5级图/城堡；Lv1-Lv9：被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：叛徒地下墓穴/继母艾莎；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：大车炮台/酷吏地下城；Lv5-Lv8：5级图/城堡；Lv1-Lv9：被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <t>Lv5-Lv10：大车炮台；Lv1-Lv10：被弃者地下城/大型被弃者地窖；</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">对稀有，独特，和传奇敌人的攻击速度提高 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">将击晕和冻结时间减少 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>减少恐惧效果持续时间</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>降低猫咪能源消耗速度的</t>
     </r>
     <r>
       <rPr>
@@ -92,445 +1582,9 @@
     </r>
   </si>
   <si>
-    <t>符文操控者</t>
-  </si>
-  <si>
-    <t>猎人</t>
-  </si>
-  <si>
-    <t>训练有素的猫咪</t>
-  </si>
-  <si>
-    <t>训练过的狼</t>
-  </si>
-  <si>
-    <t>凝固的血液</t>
-  </si>
-  <si>
-    <t>防霜</t>
-  </si>
-  <si>
-    <t>防火</t>
-  </si>
-  <si>
-    <t>设陷阱者</t>
-  </si>
-  <si>
-    <t>精力充沛</t>
-  </si>
-  <si>
-    <t>超级专注</t>
-  </si>
-  <si>
-    <t>重生</t>
-  </si>
-  <si>
-    <t>群防</t>
-  </si>
-  <si>
-    <t>无畏</t>
-  </si>
-  <si>
-    <t>势不可挡</t>
-  </si>
-  <si>
-    <t>免疫</t>
-  </si>
-  <si>
-    <t>铁胃</t>
-  </si>
-  <si>
-    <t>护火者</t>
-  </si>
-  <si>
-    <t>探路人</t>
-  </si>
-  <si>
-    <t>治疗休息</t>
-  </si>
-  <si>
-    <t>Lvl 15</t>
-  </si>
-  <si>
-    <t>Lvl 14</t>
-  </si>
-  <si>
-    <t>Lvl 13</t>
-  </si>
-  <si>
-    <t>Lvl 12</t>
-  </si>
-  <si>
-    <t>Lvl 11</t>
-  </si>
-  <si>
-    <t>Lvl 10</t>
-  </si>
-  <si>
-    <t>Lvl 9</t>
-  </si>
-  <si>
-    <t>Lvl 8</t>
-  </si>
-  <si>
-    <t>Lvl 7</t>
-  </si>
-  <si>
-    <t>Lvl 6</t>
-  </si>
-  <si>
-    <t>Lvl 5</t>
-  </si>
-  <si>
-    <t>Lvl 4</t>
-  </si>
-  <si>
-    <t>Lvl 3</t>
-  </si>
-  <si>
-    <t>Lvl 2</t>
-  </si>
-  <si>
-    <t>Lvl 1</t>
-  </si>
-  <si>
-    <t>特殊</t>
-  </si>
-  <si>
-    <t>食物强化</t>
-  </si>
-  <si>
-    <t>饮料强化</t>
-  </si>
-  <si>
-    <t>强力生命值</t>
-  </si>
-  <si>
-    <t>奔跑速度</t>
-  </si>
-  <si>
-    <t>角色</t>
-  </si>
-  <si>
-    <t>浆果</t>
-  </si>
-  <si>
-    <t>亚麻纤维</t>
-  </si>
-  <si>
-    <t>铁矿石</t>
-  </si>
-  <si>
-    <t>铜矿石</t>
-  </si>
-  <si>
-    <t>石灰岩</t>
-  </si>
-  <si>
-    <t>原桦木</t>
-  </si>
-  <si>
-    <t>原松木</t>
-  </si>
-  <si>
-    <t>资源</t>
-  </si>
-  <si>
-    <t>哈特碎片</t>
-  </si>
-  <si>
-    <t>哈利德祭祀</t>
-  </si>
-  <si>
-    <t>1%闪避概率</t>
-  </si>
-  <si>
-    <t>恐怖蝙蝠</t>
-  </si>
-  <si>
-    <t>骷髅</t>
-  </si>
-  <si>
-    <t>哀悼死神的影子</t>
-  </si>
-  <si>
-    <t>大车炮台中尉</t>
-  </si>
-  <si>
-    <t>大车炮台士兵</t>
-  </si>
-  <si>
-    <t>抄写员幽灵</t>
-  </si>
-  <si>
-    <t>科学家幽灵</t>
-  </si>
-  <si>
-    <t>被咒狂徒</t>
-  </si>
-  <si>
-    <t>被咒勇士</t>
-  </si>
-  <si>
-    <t>瘟疫缠身者</t>
-  </si>
-  <si>
-    <t>火焰守卫</t>
-  </si>
-  <si>
-    <t>残忍酷吏</t>
-  </si>
-  <si>
-    <t>惩罚者</t>
-  </si>
-  <si>
-    <t>猎头者</t>
-  </si>
-  <si>
-    <t>酷吏</t>
-  </si>
-  <si>
-    <t>女祭司</t>
-  </si>
-  <si>
-    <t>掷斧者</t>
-  </si>
-  <si>
-    <t>屠宰者</t>
-  </si>
-  <si>
-    <t>痛苦者</t>
-  </si>
-  <si>
-    <t>亵渎者</t>
-  </si>
-  <si>
-    <t>被弃者</t>
-  </si>
-  <si>
-    <t>被附身者</t>
-  </si>
-  <si>
-    <t>瘟疫之卵</t>
-  </si>
-  <si>
-    <t>麻风战士</t>
-  </si>
-  <si>
-    <t>瘟疫野蛮人</t>
-  </si>
-  <si>
-    <t>瘟疫强盗</t>
-  </si>
-  <si>
-    <t>黑暗猎人</t>
-  </si>
-  <si>
-    <t>被咒圣殿骑士</t>
-  </si>
-  <si>
-    <t>被咒骑士</t>
-  </si>
-  <si>
-    <t>恐狼</t>
-  </si>
-  <si>
-    <t>被咒者</t>
-  </si>
-  <si>
-    <t>熊</t>
-  </si>
-  <si>
-    <t>狼</t>
-  </si>
-  <si>
-    <t>麻风病人</t>
-  </si>
-  <si>
-    <t>闪避</t>
-  </si>
-  <si>
-    <t>曼德拉药酒</t>
-  </si>
-  <si>
-    <t>苦药酒</t>
-  </si>
-  <si>
-    <t>香料酒</t>
-  </si>
-  <si>
-    <t>蘑菇浸剂</t>
-  </si>
-  <si>
-    <t>蜂蜜桶</t>
-  </si>
-  <si>
-    <t>麦芽酒</t>
-  </si>
-  <si>
-    <t>绷带</t>
-  </si>
-  <si>
-    <t>牛肉干</t>
-  </si>
-  <si>
-    <t>韭葱汤</t>
-  </si>
-  <si>
-    <t>浆果饮料</t>
-  </si>
-  <si>
-    <t>烤肉</t>
-  </si>
-  <si>
-    <t>烤韭葱</t>
-  </si>
-  <si>
-    <t>治疗</t>
-  </si>
-  <si>
-    <t>弓与弩</t>
-  </si>
-  <si>
-    <t>护盾</t>
-  </si>
-  <si>
-    <t>戟</t>
-  </si>
-  <si>
-    <t>长剑</t>
-  </si>
-  <si>
-    <t>双刃大砍刀</t>
-  </si>
-  <si>
-    <t>短弯刀</t>
-  </si>
-  <si>
-    <t>战争刀</t>
-  </si>
-  <si>
-    <t>变种剑</t>
-  </si>
-  <si>
-    <t>弯刀</t>
-  </si>
-  <si>
-    <t>法兰锤</t>
-  </si>
-  <si>
-    <t>铜战斧</t>
-  </si>
-  <si>
-    <t>流星锤</t>
-  </si>
-  <si>
-    <t>尖刺锤</t>
-  </si>
-  <si>
-    <t>单手剑</t>
-  </si>
-  <si>
-    <t>浆</t>
-  </si>
-  <si>
-    <t>长柄叉</t>
-  </si>
-  <si>
-    <t>匕首</t>
-  </si>
-  <si>
-    <t>锹</t>
-  </si>
-  <si>
-    <t>铁匠锤</t>
-  </si>
-  <si>
-    <t>车把</t>
-  </si>
-  <si>
-    <t>镰刀</t>
-  </si>
-  <si>
-    <t>火把</t>
-  </si>
-  <si>
-    <t>锄头</t>
-  </si>
-  <si>
-    <t>棍子</t>
-  </si>
-  <si>
-    <t>拳头</t>
-  </si>
-  <si>
-    <t>伤害</t>
-  </si>
-  <si>
-    <t>杀死司令</t>
-  </si>
-  <si>
-    <t>诅咒</t>
-  </si>
-  <si>
-    <t>抑制</t>
-  </si>
-  <si>
-    <t>石化</t>
-  </si>
-  <si>
-    <t>防御姿态</t>
-  </si>
-  <si>
-    <t>惩罚</t>
-  </si>
-  <si>
-    <t>循环效应</t>
-  </si>
-  <si>
-    <t>眩晕一击</t>
-  </si>
-  <si>
-    <t>重击</t>
-  </si>
-  <si>
-    <t>吓跑夜游神，升级可以提高充能速度</t>
-  </si>
-  <si>
-    <t>黑暗驱逐者</t>
-  </si>
-  <si>
-    <t>渡鸦之眼</t>
-  </si>
-  <si>
-    <t>疾跑</t>
-  </si>
-  <si>
-    <t>主动技能</t>
-  </si>
-  <si>
-    <t>抗衰败</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>% 闪避概率</t>
-    </r>
-  </si>
-  <si>
+    <r>
+      <t>被攻击时有</t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -546,1075 +1600,8 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>闪避概率</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">治疗提高 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>伤害加</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>% 几率获取额外资源</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>% 几率获取额外资源</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>地点奔跑速度提高</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">最大生命值提高 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>在家里每呆上10秒，就能恢复</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>点生命值</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">饱食度最大值增加 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">饮料条最大值增加 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">将毒素伤害减少 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">减少出血造成的伤害 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>减少火焰伤害</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">将击晕和冻结时间减少 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%³</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">将地点之间的步行时间减少 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>火把燃烧时间延长</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">% </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>食物和饮料中毒抗性为</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>受到致命一击后重生概率为</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">对稀有，独特，和传奇敌人的攻击速度提高 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%³</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>能量回复速度增加</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>被困时，敌人收到伤害增加</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">你的恶狼造成的伤害增加 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>放置陷阱的速度快了</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>你重新装弩的速度快了</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>将地点奔跑速度提高</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>，持续5秒</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>进行鸟瞰，可以将视野范围提高</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>200%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>你的下次攻击造成</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>点额外伤害</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>下次攻击可使敌人击晕</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>秒</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>对方圆3米内的敌人造成</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>点纯伤害</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>反弹敌人给予的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>14%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>物理伤害，持续3秒</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>护甲提高</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>14%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>，持续5秒</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>变成石头，持续</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>秒，期间获得无敌效果并且持续治疗</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>下次攻击将减慢敌人攻击速度</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>，持续7秒</t>
-    </r>
-  </si>
-  <si>
-    <t>下次攻击会让敌人变得虚弱，收到的物理伤害增加8%，持续7秒</t>
-  </si>
-  <si>
-    <r>
-      <t>暂时提高恐狼移速60%，攻速40%，以及伤害</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>，持续7秒</t>
-    </r>
-  </si>
-  <si>
-    <t>精打细算的猎人</t>
-  </si>
-  <si>
-    <t>用工兵套件拆除陷阱后，有25%的几率将其拾起</t>
-  </si>
-  <si>
-    <t>灵巧弩手</t>
-  </si>
-  <si>
-    <t>击败目标后，有10%的几率立即装填弩</t>
-  </si>
-  <si>
-    <t>猎人之眼</t>
-  </si>
-  <si>
-    <t>使用远程武器时，视野增加50%</t>
-  </si>
-  <si>
-    <t>如果附近有一个以上的敌人，护甲提高5</t>
-  </si>
-  <si>
-    <t>熟练的珠宝匠</t>
-  </si>
-  <si>
-    <t>激活时有1%的几率保留护符的奶就度</t>
-  </si>
-  <si>
-    <r>
-      <t>减少寒冷伤害</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>减少衰败造成的伤害</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>减少恐惧效果持续时间</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%（1-4级在破损大车/堕落骑士）</t>
-    </r>
-  </si>
-  <si>
-    <t>青铜矛</t>
-  </si>
-  <si>
-    <t>狂战士战斧</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">所有护盾耐用度增加 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>一次发射两支箭的概率为</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%</t>
-    </r>
-  </si>
-  <si>
-    <t>冰环</t>
-  </si>
-  <si>
-    <t>短暂冻结附近敌人，目标数量：1</t>
-  </si>
-  <si>
-    <t>治疗提高 2</t>
-  </si>
-  <si>
-    <t>治疗提高2</t>
-  </si>
-  <si>
-    <t>掉落地点</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10: 古人墓穴；</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>降低猫咪能源消耗速度的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>（1-4级在破损大车/堕落骑士）</t>
-    </r>
-  </si>
-  <si>
-    <t>增加召唤生物的生命值5%</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：哈利德；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：哈特；</t>
-  </si>
-  <si>
-    <t>弗拉格纳的侍女</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：弗拉格纳；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：大车炮台；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10: 古人墓穴/大车炮台；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：西方银矿/继母艾莎；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：继母艾莎；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：西方银矿；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10: 古人墓穴/西方银矿；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：看守者棚屋；Lv1-Lv10：大车炮台；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv4：看守者棚屋；Lv1-Lv10：大车炮台；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：游商</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：游商/酷吏地下城</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：酷吏地下城；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：酷吏地下城；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：被诅咒的天文台</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：叛徒地下墓穴；Lv1-Lv10: 古人墓穴/酷吏地下城；Lv5-Lv10：大车炮台；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：叛徒地下墓穴；Lv5-Lv10：大车炮台；Lv1-Lv10：酷吏地下城</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：酷吏地下城；Lv1-Lv8：叛徒地下墓穴</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：城堡</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：大车炮台/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：4级图；Lv5-Lv10：5级图；Lv1-Lv10：城堡</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：4级图；Lv1-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：4级图；Lv1-Lv7：5级图/城堡；Lv6-Lv10：酷吏地下城；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：酷吏地下城；Lv1-Lv6：被诅咒的天文台</t>
-  </si>
-  <si>
-    <t>Lv1-Lv4：4级图；Lv1-Lv8：5级图/城堡；Lv5-Lv10：大车炮台；Lv6-Lv10：酷吏地下城</t>
-  </si>
-  <si>
-    <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士</t>
-  </si>
-  <si>
-    <t>Lv1-Lv6：叛徒地下墓穴；Lv7-Lv8：商人护送；Lv1-Lv8：酷吏地下城</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：死灵法师的巢穴；Lv1-Lv10: 古人墓穴/西方银矿/被诅咒的天文台；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：死灵法师的巢穴；Lv1-Lv10：西方银矿/继母艾莎；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv4：1-3级图/墓地之夜；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv8：哈特/弗拉格纳；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：继母艾莎</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：死灵法师的巢穴；Lv1-Lv10: 古人墓穴/西方银矿/继母艾莎；</t>
-  </si>
-  <si>
-    <t>Lv5-Lv10：大车炮台；Lv1-Lv9：继母艾莎；Lv6-Lv10：酷吏地下城</t>
-  </si>
-  <si>
-    <t>待测</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>%闪避概率</t>
-    </r>
-  </si>
-  <si>
-    <t>Lv1：哈利德/哈特/弗拉格纳/1-3级图/地下神祠/墓地之夜/小型被弃者地窖/被弃者地窖；Lv1-Lv2：4级图/5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：哈利德/哈特/弗拉格纳/1-3级图/地下神祠/墓地之夜/小型被弃者地窖/被弃者地窖；Lv2-Lv3：4级图/5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：地下神祠/墓地之夜/小型被弃者地窖；Lv1-Lv3：哈利德/哈特/弗拉格纳/1-3级图/被弃者地窖；Lv3-Lv4：4级图/5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：地下神祠/墓地之夜/小型被弃者地窖；Lv1-Lv4：哈利德/哈特/弗拉格纳/1-3级图/被弃者地窖；Lv4-Lv5：4级图/5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：1-3级图/小型被弃者地窖/被弃者地窖；Lv1-Lv4：墓地之夜；Lv4-Lv7：被弃者地下城/大型被弃者地窖；Lv5-Lv7：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：1-3级图/小型被弃者地窖/被弃者地窖；Lv1-Lv4：墓地之夜；Lv5-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；Lv1-Lv10：被诅咒的天文台</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：5级图/城堡；Lv1-Lv10：大车炮台；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv8：4级图；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv7-Lv8：商人护送；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv7：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv7：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv8：4级图；Lv5-Lv10：5级图/城堡；Lv1-Lv10：大车炮台；</t>
-  </si>
-  <si>
-    <t>Lv1：野蛮人营地；Lv1-Lv10: 古人墓穴/被弃者地下城/大型被弃者地窖；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv10：被弃者地下城/大型被弃者地窖；Lv3-Lv5：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv6：4级图；Lv5-Lv8：5级图/城堡；Lv1-Lv10：被诅咒的天文台</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：1-3级图/小型被弃者地窖/被弃者地窖；Lv1-Lv4：墓地之夜；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：大车炮台/被弃者地下城/大型被弃者地窖；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士；Lv1-Lv10：被弃者地下城/大型被弃者地窖；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：被弃者地下城/地下神祠/堕落骑士/大型被弃者地窖；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/铜矿/墓地之夜/被弃者地窖；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv8：小型被弃者地窖；Lv1-Lv10：被弃者地窖/大型被弃者地窖；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv8：小型被弃者地窖；Lv1-Lv10：继母艾莎/被弃者地窖/大型被弃者地窖；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv8：小型被弃者地窖/被弃者地窖；Lv1-Lv10：继母艾莎/大型被弃者地窖</t>
-  </si>
-  <si>
-    <t>Lv1-Lv4：被弃者地窖；Lv1-Lv10：继母艾莎/大型被弃者地窖</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv10：被弃者地下城/大型被弃者地窖；Lv3-Lv6：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv7：4级图；Lv5-Lv8：5级图/城堡；Lv1-Lv10：大车炮台；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv4：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv8：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv8：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv5-Lv9：4级图；Lv5-Lv10：5级图/城堡；Lv1-Lv10：大车炮台；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv3-Lv5：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv5-Lv6：4级图；Lv3-Lv10：被弃者地下城；Lv5-Lv8：城堡；Lv3-Lv10：大型被弃者地窖</t>
-  </si>
-  <si>
-    <t>Lv1-Lv10：大车炮台被弃者地下城/大型被弃者地窖；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士；Lv1-Lv10: 古人墓穴/大车炮台/被弃者地下城/大型被弃者地窖；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：哈利德/哈特/弗拉格纳/被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：哈利德/哈特/弗拉格纳/被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；Lv1-Lv10：被诅咒的天文台</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv4-Lv5：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv5：被弃者地下城/地下神祠/大型被弃者地窖；Lv1-Lv6：哈利德/哈特/弗拉格纳；Lv5-Lv6：4级图/5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv5-Lv7：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：被弃者地下城/酷吏地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv5-Lv8：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv1-Lv9：被弃者地下城/大型被弃者地窖；Lv5-Lv8：5级图/城堡；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：叛徒地下墓穴/继母艾莎；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：4级图；Lv5-Lv10：大车炮台/酷吏地下城；Lv5-Lv8：5级图/城堡；Lv1-Lv9：被弃者地下城/大型被弃者地窖；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv5-Lv6：叛徒地下墓穴/继母艾莎；Lv1-Lv6：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv10：大车炮台/酷吏地下城；Lv5-Lv8：5级图/城堡；Lv1-Lv9：被弃者地下城/大型被弃者地窖；</t>
-  </si>
-  <si>
-    <t>Lv5-Lv10：大车炮台；Lv1-Lv10：被弃者地下城/大型被弃者地窖；</t>
+      <t>的几率给护盾瞬间充能</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3141,63 +3128,63 @@
     <row r="1" spans="2:21" ht="14.65" thickBot="1"/>
     <row r="2" spans="2:21" ht="14.65" thickTop="1">
       <c r="B2" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H2" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J2" s="39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K2" s="39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L2" s="39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M2" s="41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N2" s="41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O2" s="41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P2" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q2" s="64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R2" s="59" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="2:21" ht="41.65">
       <c r="B3" s="81" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D3" s="23">
         <v>0.12</v>
@@ -3232,15 +3219,15 @@
       <c r="P3" s="35"/>
       <c r="Q3" s="35"/>
       <c r="R3" s="68" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="2:21" ht="41.65">
       <c r="B4" s="82" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D4" s="22">
         <v>2.5</v>
@@ -3275,15 +3262,15 @@
       <c r="P4" s="35"/>
       <c r="Q4" s="35"/>
       <c r="R4" s="68" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="2:21" ht="41.65">
       <c r="B5" s="82" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D5" s="53"/>
       <c r="E5" s="53"/>
@@ -3300,15 +3287,15 @@
       <c r="P5" s="53"/>
       <c r="Q5" s="65"/>
       <c r="R5" s="68" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="2:21" ht="41.65">
       <c r="B6" s="82" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D6" s="6">
         <v>15</v>
@@ -3353,15 +3340,15 @@
         <v>90</v>
       </c>
       <c r="R6" s="68" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="2:21">
       <c r="B7" s="82" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D7" s="6">
         <v>0.75</v>
@@ -3406,15 +3393,15 @@
         <v>4.2</v>
       </c>
       <c r="R7" s="68" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="2:21" ht="41.65">
       <c r="B8" s="82" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D8" s="6">
         <v>6</v>
@@ -3459,15 +3446,15 @@
         <v>36</v>
       </c>
       <c r="R8" s="68" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="2:21" ht="41.65">
       <c r="B9" s="82" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D9" s="22">
         <v>0.21</v>
@@ -3512,15 +3499,15 @@
         <v>1.2</v>
       </c>
       <c r="R9" s="68" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="2:21" ht="41.65">
       <c r="B10" s="82" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D10" s="22">
         <v>0.21</v>
@@ -3565,15 +3552,15 @@
         <v>1.2</v>
       </c>
       <c r="R10" s="68" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="2:21">
       <c r="B11" s="82" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D11" s="6">
         <v>2</v>
@@ -3618,15 +3605,15 @@
         <v>15</v>
       </c>
       <c r="R11" s="68" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="2:21">
       <c r="B12" s="82" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D12" s="22">
         <v>0.12</v>
@@ -3671,15 +3658,15 @@
         <v>0.6</v>
       </c>
       <c r="R12" s="68" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="2:21">
       <c r="B13" s="82" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D13" s="22">
         <v>0.12</v>
@@ -3724,15 +3711,15 @@
         <v>0.6</v>
       </c>
       <c r="R13" s="68" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="2:21">
       <c r="B14" s="83" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D14" s="7">
         <v>2</v>
@@ -3777,15 +3764,15 @@
         <v>15</v>
       </c>
       <c r="R14" s="68" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="2:21" ht="14.65" thickBot="1">
       <c r="B15" s="84" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D15" s="57">
         <v>2</v>
@@ -3830,7 +3817,7 @@
         <v>15</v>
       </c>
       <c r="R15" s="69" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="U15" s="55"/>
     </row>
@@ -3854,63 +3841,63 @@
     </row>
     <row r="17" spans="2:20" ht="14.65" thickTop="1">
       <c r="B17" s="36" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H17" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I17" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J17" s="39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K17" s="39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L17" s="39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M17" s="41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N17" s="41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O17" s="41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P17" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q17" s="64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R17" s="59" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="2:20">
       <c r="B18" s="100" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D18" s="12">
         <v>2</v>
@@ -3929,15 +3916,15 @@
       <c r="P18" s="35"/>
       <c r="Q18" s="35"/>
       <c r="R18" s="68" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" spans="2:20">
       <c r="B19" s="101" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D19" s="6">
         <v>2</v>
@@ -3958,15 +3945,15 @@
       <c r="P19" s="35"/>
       <c r="Q19" s="35"/>
       <c r="R19" s="68" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="2:20">
       <c r="B20" s="101" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D20" s="6">
         <v>2</v>
@@ -3987,15 +3974,15 @@
       <c r="P20" s="35"/>
       <c r="Q20" s="35"/>
       <c r="R20" s="68" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="2:20">
       <c r="B21" s="101" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D21" s="6">
         <v>2</v>
@@ -4016,15 +4003,15 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
       <c r="R21" s="68" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="2:20" ht="27.75">
       <c r="B22" s="101" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D22" s="6">
         <v>2</v>
@@ -4047,15 +4034,15 @@
       <c r="P22" s="35"/>
       <c r="Q22" s="35"/>
       <c r="R22" s="68" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="2:20" ht="27.75">
       <c r="B23" s="101" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D23" s="6">
         <v>2</v>
@@ -4078,15 +4065,15 @@
       <c r="P23" s="35"/>
       <c r="Q23" s="35"/>
       <c r="R23" s="68" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="2:20" ht="27.75">
       <c r="B24" s="101" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D24" s="6">
         <v>2</v>
@@ -4111,15 +4098,15 @@
       <c r="P24" s="35"/>
       <c r="Q24" s="35"/>
       <c r="R24" s="68" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="2:20" ht="27.75">
       <c r="B25" s="101" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D25" s="6">
         <v>2</v>
@@ -4144,15 +4131,15 @@
       <c r="P25" s="35"/>
       <c r="Q25" s="35"/>
       <c r="R25" s="68" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" spans="2:20" ht="27.75">
       <c r="B26" s="101" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D26" s="6">
         <v>2</v>
@@ -4177,15 +4164,15 @@
       <c r="P26" s="35"/>
       <c r="Q26" s="35"/>
       <c r="R26" s="68" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="27" spans="2:20" ht="27.75">
       <c r="B27" s="101" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D27" s="6">
         <v>2</v>
@@ -4212,15 +4199,15 @@
       <c r="P27" s="35"/>
       <c r="Q27" s="35"/>
       <c r="R27" s="68" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="2:20" ht="27.75">
       <c r="B28" s="101" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D28" s="6">
         <v>2</v>
@@ -4247,15 +4234,15 @@
       <c r="P28" s="35"/>
       <c r="Q28" s="35"/>
       <c r="R28" s="68" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="29" spans="2:20" ht="27.75">
       <c r="B29" s="101" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D29" s="6">
         <v>2</v>
@@ -4282,15 +4269,15 @@
       <c r="P29" s="35"/>
       <c r="Q29" s="35"/>
       <c r="R29" s="68" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" spans="2:20" ht="42" thickBot="1">
       <c r="B30" s="101" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D30" s="6">
         <v>2</v>
@@ -4319,15 +4306,15 @@
       <c r="P30" s="35"/>
       <c r="Q30" s="35"/>
       <c r="R30" s="68" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="31" spans="2:20" ht="42" thickBot="1">
       <c r="B31" s="101" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D31" s="6">
         <v>2</v>
@@ -4358,16 +4345,16 @@
       <c r="P31" s="35"/>
       <c r="Q31" s="35"/>
       <c r="R31" s="68" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="T31" s="52"/>
     </row>
     <row r="32" spans="2:20">
       <c r="B32" s="101" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D32" s="6">
         <v>2</v>
@@ -4398,15 +4385,15 @@
       <c r="P32" s="35"/>
       <c r="Q32" s="35"/>
       <c r="R32" s="68" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="2:18" ht="41.65">
       <c r="B33" s="101" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D33" s="6">
         <v>2</v>
@@ -4437,15 +4424,15 @@
       <c r="P33" s="35"/>
       <c r="Q33" s="35"/>
       <c r="R33" s="68" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="2:18" ht="27.75">
       <c r="B34" s="101" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D34" s="6">
         <v>2</v>
@@ -4478,15 +4465,15 @@
       <c r="P34" s="35"/>
       <c r="Q34" s="35"/>
       <c r="R34" s="68" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35" spans="2:18">
       <c r="B35" s="101" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D35" s="6">
         <v>2</v>
@@ -4531,15 +4518,15 @@
         <v>15</v>
       </c>
       <c r="R35" s="71" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="2:18" ht="41.65">
       <c r="B36" s="101" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D36" s="6">
         <v>2</v>
@@ -4584,15 +4571,15 @@
         <v>15</v>
       </c>
       <c r="R36" s="68" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" spans="2:18">
       <c r="B37" s="101" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D37" s="6">
         <v>2</v>
@@ -4637,15 +4624,15 @@
         <v>15</v>
       </c>
       <c r="R37" s="71" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="2:18" ht="41.65">
       <c r="B38" s="101" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D38" s="6">
         <v>2</v>
@@ -4690,15 +4677,15 @@
         <v>15</v>
       </c>
       <c r="R38" s="68" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39" spans="2:18">
       <c r="B39" s="101" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D39" s="6">
         <v>2</v>
@@ -4743,15 +4730,15 @@
         <v>15</v>
       </c>
       <c r="R39" s="71" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40" spans="2:18">
       <c r="B40" s="101" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D40" s="6">
         <v>2</v>
@@ -4796,15 +4783,15 @@
         <v>15</v>
       </c>
       <c r="R40" s="71" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41" spans="2:18">
       <c r="B41" s="101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D41" s="6">
         <v>2</v>
@@ -4849,15 +4836,15 @@
         <v>15</v>
       </c>
       <c r="R41" s="71" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="2:18">
       <c r="B42" s="101" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D42" s="22">
         <v>0.04</v>
@@ -4902,15 +4889,15 @@
         <v>0.3</v>
       </c>
       <c r="R42" s="71" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43" spans="2:18">
       <c r="B43" s="102" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D43" s="8">
         <v>0.06</v>
@@ -4955,15 +4942,15 @@
         <v>0.4</v>
       </c>
       <c r="R43" s="71" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="44" spans="2:18" ht="14.65" thickBot="1">
       <c r="B44" s="103" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D44" s="18">
         <v>2</v>
@@ -5008,7 +4995,7 @@
         <v>15</v>
       </c>
       <c r="R44" s="72" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45" spans="2:18" ht="15" thickTop="1" thickBot="1">
@@ -5031,63 +5018,63 @@
     </row>
     <row r="46" spans="2:18" ht="14.65" thickTop="1">
       <c r="B46" s="36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G46" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H46" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I46" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J46" s="40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K46" s="40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L46" s="40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M46" s="41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N46" s="41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O46" s="41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P46" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q46" s="64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R46" s="59" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="47" spans="2:18" ht="42.75">
       <c r="B47" s="85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D47" s="12">
         <v>2</v>
@@ -5122,15 +5109,15 @@
       <c r="P47" s="35"/>
       <c r="Q47" s="35"/>
       <c r="R47" s="73" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" spans="2:18" ht="42.75">
       <c r="B48" s="86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D48" s="6">
         <v>2</v>
@@ -5165,15 +5152,15 @@
       <c r="P48" s="35"/>
       <c r="Q48" s="35"/>
       <c r="R48" s="73" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="49" spans="2:18" ht="42.75">
       <c r="B49" s="86" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D49" s="6">
         <v>2</v>
@@ -5208,15 +5195,15 @@
       <c r="P49" s="35"/>
       <c r="Q49" s="35"/>
       <c r="R49" s="73" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="50" spans="2:18" ht="42.75">
       <c r="B50" s="86" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D50" s="6">
         <v>2</v>
@@ -5251,15 +5238,15 @@
       <c r="P50" s="35"/>
       <c r="Q50" s="35"/>
       <c r="R50" s="73" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="51" spans="2:18" ht="42.75">
       <c r="B51" s="86" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D51" s="6">
         <v>2</v>
@@ -5294,15 +5281,15 @@
       <c r="P51" s="35"/>
       <c r="Q51" s="35"/>
       <c r="R51" s="73" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="52" spans="2:18" ht="42.75">
       <c r="B52" s="86" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D52" s="6">
         <v>2</v>
@@ -5337,15 +5324,15 @@
       <c r="P52" s="35"/>
       <c r="Q52" s="35"/>
       <c r="R52" s="73" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="53" spans="2:18" ht="42.75">
       <c r="B53" s="86" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D53" s="6">
         <v>3</v>
@@ -5380,15 +5367,15 @@
       <c r="P53" s="35"/>
       <c r="Q53" s="35"/>
       <c r="R53" s="73" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="54" spans="2:18" ht="42.75">
       <c r="B54" s="86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D54" s="6">
         <v>3</v>
@@ -5423,15 +5410,15 @@
       <c r="P54" s="35"/>
       <c r="Q54" s="35"/>
       <c r="R54" s="73" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="55" spans="2:18">
       <c r="B55" s="86" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D55" s="6">
         <v>4</v>
@@ -5458,15 +5445,15 @@
       <c r="P55" s="35"/>
       <c r="Q55" s="35"/>
       <c r="R55" s="71" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="56" spans="2:18">
       <c r="B56" s="86" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D56" s="6">
         <v>4</v>
@@ -5493,15 +5480,15 @@
       <c r="P56" s="35"/>
       <c r="Q56" s="35"/>
       <c r="R56" s="71" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="57" spans="2:18">
       <c r="B57" s="86" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D57" s="6">
         <v>4</v>
@@ -5528,15 +5515,15 @@
       <c r="P57" s="35"/>
       <c r="Q57" s="35"/>
       <c r="R57" s="71" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="58" spans="2:18" ht="14.65" thickBot="1">
       <c r="B58" s="87" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D58" s="18">
         <v>4</v>
@@ -5563,7 +5550,7 @@
       <c r="P58" s="48"/>
       <c r="Q58" s="48"/>
       <c r="R58" s="72" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="59" spans="2:18" ht="15" thickTop="1" thickBot="1">
@@ -5586,63 +5573,63 @@
     </row>
     <row r="60" spans="2:18" ht="14.65" thickTop="1">
       <c r="B60" s="36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C60" s="37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D60" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E60" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F60" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G60" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H60" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I60" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J60" s="40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K60" s="40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L60" s="40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M60" s="41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N60" s="41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O60" s="41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P60" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q60" s="64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R60" s="59" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="61" spans="2:18" ht="28.5">
       <c r="B61" s="93" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D61" s="12">
         <v>2</v>
@@ -5677,15 +5664,15 @@
       <c r="P61" s="35"/>
       <c r="Q61" s="35"/>
       <c r="R61" s="73" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="62" spans="2:18" ht="28.5">
       <c r="B62" s="94" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D62" s="6">
         <v>2</v>
@@ -5720,15 +5707,15 @@
       <c r="P62" s="35"/>
       <c r="Q62" s="35"/>
       <c r="R62" s="73" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="63" spans="2:18" ht="28.5">
       <c r="B63" s="94" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D63" s="6">
         <v>2</v>
@@ -5763,15 +5750,15 @@
       <c r="P63" s="35"/>
       <c r="Q63" s="35"/>
       <c r="R63" s="73" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="64" spans="2:18" ht="28.5">
       <c r="B64" s="94" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D64" s="6">
         <v>2</v>
@@ -5806,15 +5793,15 @@
       <c r="P64" s="35"/>
       <c r="Q64" s="35"/>
       <c r="R64" s="73" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="65" spans="2:18" ht="28.5">
       <c r="B65" s="94" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D65" s="6">
         <v>2</v>
@@ -5849,15 +5836,15 @@
       <c r="P65" s="35"/>
       <c r="Q65" s="35"/>
       <c r="R65" s="73" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="66" spans="2:18" ht="28.5">
       <c r="B66" s="94" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D66" s="6">
         <v>2</v>
@@ -5892,15 +5879,15 @@
       <c r="P66" s="35"/>
       <c r="Q66" s="35"/>
       <c r="R66" s="73" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="67" spans="2:18" ht="28.5">
       <c r="B67" s="94" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D67" s="6">
         <v>2</v>
@@ -5935,15 +5922,15 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="35"/>
       <c r="R67" s="73" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="68" spans="2:18">
       <c r="B68" s="94" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D68" s="6">
         <v>2</v>
@@ -5978,15 +5965,15 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="35"/>
       <c r="R68" s="71" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="69" spans="2:18">
       <c r="B69" s="94" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D69" s="6">
         <v>2</v>
@@ -6021,15 +6008,15 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
       <c r="R69" s="71" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="70" spans="2:18">
       <c r="B70" s="94" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D70" s="6">
         <v>2</v>
@@ -6064,15 +6051,15 @@
       <c r="P70" s="35"/>
       <c r="Q70" s="35"/>
       <c r="R70" s="71" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="71" spans="2:18">
       <c r="B71" s="94" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D71" s="6">
         <v>2</v>
@@ -6107,15 +6094,15 @@
       <c r="P71" s="35"/>
       <c r="Q71" s="35"/>
       <c r="R71" s="71" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="72" spans="2:18">
       <c r="B72" s="94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D72" s="6">
         <v>2</v>
@@ -6150,15 +6137,15 @@
       <c r="P72" s="35"/>
       <c r="Q72" s="35"/>
       <c r="R72" s="71" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="73" spans="2:18">
       <c r="B73" s="94" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D73" s="6">
         <v>2</v>
@@ -6193,15 +6180,15 @@
       <c r="P73" s="35"/>
       <c r="Q73" s="35"/>
       <c r="R73" s="71" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="74" spans="2:18">
       <c r="B74" s="94" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D74" s="6">
         <v>2</v>
@@ -6236,15 +6223,15 @@
       <c r="P74" s="35"/>
       <c r="Q74" s="35"/>
       <c r="R74" s="71" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="75" spans="2:18">
       <c r="B75" s="94" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D75" s="6">
         <v>2</v>
@@ -6279,15 +6266,15 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="35"/>
       <c r="R75" s="71" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="76" spans="2:18">
       <c r="B76" s="94" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D76" s="6">
         <v>2</v>
@@ -6322,15 +6309,15 @@
       <c r="P76" s="35"/>
       <c r="Q76" s="35"/>
       <c r="R76" s="71" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="2:18">
       <c r="B77" s="94" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D77" s="6">
         <v>2</v>
@@ -6365,15 +6352,15 @@
       <c r="P77" s="35"/>
       <c r="Q77" s="35"/>
       <c r="R77" s="71" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="78" spans="2:18">
       <c r="B78" s="94" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D78" s="6">
         <v>2</v>
@@ -6408,15 +6395,15 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
       <c r="R78" s="71" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="79" spans="2:18">
       <c r="B79" s="94" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D79" s="6">
         <v>2</v>
@@ -6451,15 +6438,15 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
       <c r="R79" s="71" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="80" spans="2:18">
       <c r="B80" s="94" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D80" s="6">
         <v>2</v>
@@ -6494,15 +6481,15 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
       <c r="R80" s="71" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="81" spans="2:18">
       <c r="B81" s="94" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D81" s="6">
         <v>2</v>
@@ -6537,15 +6524,15 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
       <c r="R81" s="71" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" spans="2:18">
       <c r="B82" s="94" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D82" s="6">
         <v>2</v>
@@ -6580,15 +6567,15 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
       <c r="R82" s="71" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="83" spans="2:18">
       <c r="B83" s="94" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D83" s="6">
         <v>2</v>
@@ -6623,15 +6610,15 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
       <c r="R83" s="71" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="84" spans="2:18">
       <c r="B84" s="94" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D84" s="6">
         <v>2</v>
@@ -6666,15 +6653,15 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
       <c r="R84" s="71" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" spans="2:18" ht="28.5">
       <c r="B85" s="94" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D85" s="6">
         <v>2</v>
@@ -6709,15 +6696,15 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
       <c r="R85" s="73" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="86" spans="2:18" ht="28.5">
       <c r="B86" s="94" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D86" s="13">
         <v>2</v>
@@ -6752,15 +6739,15 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
       <c r="R86" s="73" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="87" spans="2:18" ht="28.5">
       <c r="B87" s="95" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D87" s="14">
         <v>2</v>
@@ -6795,15 +6782,15 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
       <c r="R87" s="73" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="88" spans="2:18">
       <c r="B88" s="94" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D88" s="14">
         <v>2</v>
@@ -6838,15 +6825,15 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
       <c r="R88" s="71" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="89" spans="2:18">
       <c r="B89" s="94" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D89" s="17">
         <v>2</v>
@@ -6881,15 +6868,15 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
       <c r="R89" s="71" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="90" spans="2:18">
       <c r="B90" s="95" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D90" s="13">
         <v>2</v>
@@ -6924,15 +6911,15 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
       <c r="R90" s="71" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="91" spans="2:18">
       <c r="B91" s="95" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D91" s="13">
         <v>2</v>
@@ -6967,15 +6954,15 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
       <c r="R91" s="71" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="92" spans="2:18">
       <c r="B92" s="95" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D92" s="13">
         <v>2</v>
@@ -7010,15 +6997,15 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
       <c r="R92" s="71" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="93" spans="2:18">
       <c r="B93" s="95" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D93" s="13">
         <v>2</v>
@@ -7053,15 +7040,15 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
       <c r="R93" s="71" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="94" spans="2:18">
       <c r="B94" s="95" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D94" s="13">
         <v>2</v>
@@ -7096,15 +7083,15 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
       <c r="R94" s="71" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="95" spans="2:18">
       <c r="B95" s="95" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D95" s="13">
         <v>2</v>
@@ -7139,15 +7126,15 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
       <c r="R95" s="71" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="96" spans="2:18">
       <c r="B96" s="95" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D96" s="13">
         <v>2</v>
@@ -7182,15 +7169,15 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
       <c r="R96" s="71" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="97" spans="2:18" ht="14.65" thickBot="1">
       <c r="B97" s="96" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C97" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D97" s="18">
         <v>2</v>
@@ -7225,69 +7212,69 @@
       <c r="P97" s="48"/>
       <c r="Q97" s="48"/>
       <c r="R97" s="72" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="2:18" ht="15" thickTop="1" thickBot="1"/>
     <row r="99" spans="2:18" ht="14.65" thickTop="1">
       <c r="B99" s="36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C99" s="37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D99" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E99" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F99" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G99" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H99" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I99" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J99" s="40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K99" s="40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L99" s="40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M99" s="41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N99" s="41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O99" s="41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P99" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q99" s="64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R99" s="59" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="100" spans="2:18" ht="42.75">
       <c r="B100" s="97" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D100" s="23">
         <v>0.18</v>
@@ -7322,15 +7309,15 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
       <c r="R100" s="73" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101" spans="2:18">
       <c r="B101" s="98" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D101" s="22">
         <v>0.18</v>
@@ -7365,15 +7352,15 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
       <c r="R101" s="71" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="102" spans="2:18" ht="42.75">
       <c r="B102" s="98" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D102" s="23">
         <v>0.18</v>
@@ -7408,15 +7395,15 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
       <c r="R102" s="73" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="103" spans="2:18" ht="42.75">
       <c r="B103" s="98" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D103" s="23">
         <v>0.18</v>
@@ -7451,15 +7438,15 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
       <c r="R103" s="73" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="104" spans="2:18">
       <c r="B104" s="98" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D104" s="22">
         <v>0.18</v>
@@ -7494,15 +7481,15 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
       <c r="R104" s="71" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="105" spans="2:18" ht="42.75">
       <c r="B105" s="98" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D105" s="22">
         <v>0.08</v>
@@ -7537,15 +7524,15 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
       <c r="R105" s="73" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="106" spans="2:18" ht="43.15" thickBot="1">
       <c r="B106" s="99" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C106" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D106" s="26">
         <v>0.18</v>
@@ -7580,69 +7567,69 @@
       <c r="P106" s="48"/>
       <c r="Q106" s="48"/>
       <c r="R106" s="74" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="107" spans="2:18" ht="15" thickTop="1" thickBot="1"/>
     <row r="108" spans="2:18" ht="14.65" thickTop="1">
       <c r="B108" s="36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C108" s="37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D108" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E108" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F108" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G108" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H108" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I108" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J108" s="40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K108" s="40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L108" s="40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M108" s="41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N108" s="41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O108" s="41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P108" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q108" s="42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R108" s="59" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="109" spans="2:18" ht="42.75">
       <c r="B109" s="88" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D109" s="12">
         <v>2</v>
@@ -7677,15 +7664,15 @@
       <c r="P109" s="4"/>
       <c r="Q109" s="43"/>
       <c r="R109" s="73" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="110" spans="2:18" ht="42.75">
       <c r="B110" s="89" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D110" s="6">
         <v>4</v>
@@ -7730,15 +7717,15 @@
         <v>30</v>
       </c>
       <c r="R110" s="73" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="111" spans="2:18" ht="42.75">
       <c r="B111" s="88" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D111" s="12">
         <v>2</v>
@@ -7773,15 +7760,15 @@
       <c r="P111" s="4"/>
       <c r="Q111" s="43"/>
       <c r="R111" s="73" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="112" spans="2:18" ht="28.5">
       <c r="B112" s="89" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D112" s="6">
         <v>20</v>
@@ -7816,15 +7803,15 @@
       <c r="P112" s="4"/>
       <c r="Q112" s="43"/>
       <c r="R112" s="73" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="113" spans="2:20" ht="42.75">
       <c r="B113" s="90" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D113" s="7">
         <v>4</v>
@@ -7859,15 +7846,15 @@
       <c r="P113" s="5"/>
       <c r="Q113" s="45"/>
       <c r="R113" s="73" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="114" spans="2:20" ht="42.75">
       <c r="B114" s="88" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D114" s="12">
         <v>4</v>
@@ -7902,15 +7889,15 @@
       <c r="P114" s="4"/>
       <c r="Q114" s="43"/>
       <c r="R114" s="73" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="115" spans="2:20">
       <c r="B115" s="89" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D115" s="22">
         <v>0.08</v>
@@ -7955,15 +7942,15 @@
         <v>0.5</v>
       </c>
       <c r="R115" s="71" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="116" spans="2:20">
       <c r="B116" s="91" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D116" s="22">
         <v>0.04</v>
@@ -8008,15 +7995,15 @@
         <v>0.3</v>
       </c>
       <c r="R116" s="71" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="117" spans="2:20">
       <c r="B117" s="91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D117" s="22">
         <v>0.02</v>
@@ -8061,15 +8048,15 @@
         <v>0.15</v>
       </c>
       <c r="R117" s="71" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="118" spans="2:20" ht="14.65" thickBot="1">
       <c r="B118" s="91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D118" s="22">
         <v>0.02</v>
@@ -8114,15 +8101,15 @@
         <v>0.15</v>
       </c>
       <c r="R118" s="71" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="119" spans="2:20" ht="14.65" thickBot="1">
       <c r="B119" s="91" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D119" s="22">
         <v>0.02</v>
@@ -8167,16 +8154,16 @@
         <v>0.15</v>
       </c>
       <c r="R119" s="71" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="T119" s="52"/>
     </row>
     <row r="120" spans="2:20">
       <c r="B120" s="89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>161</v>
+        <v>278</v>
       </c>
       <c r="D120" s="22">
         <v>0.08</v>
@@ -8211,15 +8198,15 @@
       <c r="P120" s="35"/>
       <c r="Q120" s="47"/>
       <c r="R120" s="71" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="121" spans="2:20" ht="14.65" thickBot="1">
       <c r="B121" s="92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>194</v>
+        <v>279</v>
       </c>
       <c r="D121" s="26">
         <v>0.08</v>
@@ -8254,69 +8241,69 @@
       <c r="P121" s="48"/>
       <c r="Q121" s="49"/>
       <c r="R121" s="72" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122" spans="2:20" ht="15" thickTop="1" thickBot="1"/>
     <row r="123" spans="2:20" ht="14.65" thickTop="1">
       <c r="B123" s="36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C123" s="37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D123" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E123" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F123" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G123" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H123" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I123" s="39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J123" s="40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K123" s="40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L123" s="40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M123" s="41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N123" s="41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O123" s="41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P123" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q123" s="42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R123" s="59" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="124" spans="2:20" ht="42.75">
       <c r="B124" s="105" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D124" s="22">
         <v>0.06</v>
@@ -8351,15 +8338,15 @@
       <c r="P124" s="4"/>
       <c r="Q124" s="43"/>
       <c r="R124" s="63" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="125" spans="2:20" ht="28.5">
       <c r="B125" s="105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D125" s="22">
         <v>0.4</v>
@@ -8394,15 +8381,15 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="43"/>
       <c r="R125" s="63" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="126" spans="2:20" ht="28.5">
       <c r="B126" s="105" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D126" s="6">
         <v>10</v>
@@ -8437,15 +8424,15 @@
       <c r="P126" s="4"/>
       <c r="Q126" s="43"/>
       <c r="R126" s="63" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="127" spans="2:20">
       <c r="B127" s="105" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D127" s="22">
         <v>0.02</v>
@@ -8480,15 +8467,15 @@
       <c r="P127" s="4"/>
       <c r="Q127" s="43"/>
       <c r="R127" s="56" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="128" spans="2:20">
       <c r="B128" s="105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>166</v>
+        <v>277</v>
       </c>
       <c r="D128" s="22">
         <v>0.04</v>
@@ -8513,15 +8500,15 @@
       <c r="P128" s="4"/>
       <c r="Q128" s="43"/>
       <c r="R128" s="56" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="129" spans="2:18">
       <c r="B129" s="105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D129" s="22">
         <v>0.04</v>
@@ -8556,15 +8543,15 @@
       <c r="P129" s="4"/>
       <c r="Q129" s="43"/>
       <c r="R129" s="56" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="130" spans="2:18">
       <c r="B130" s="105" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D130" s="22">
         <v>0.04</v>
@@ -8599,15 +8586,15 @@
       <c r="P130" s="4"/>
       <c r="Q130" s="43"/>
       <c r="R130" s="56" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="131" spans="2:18">
       <c r="B131" s="105" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D131" s="6">
         <v>2</v>
@@ -8652,15 +8639,15 @@
         <v>15</v>
       </c>
       <c r="R131" s="56" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="132" spans="2:18">
       <c r="B132" s="105" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>205</v>
+        <v>280</v>
       </c>
       <c r="D132" s="22">
         <v>0.06</v>
@@ -8705,15 +8692,15 @@
         <v>0.2</v>
       </c>
       <c r="R132" s="56" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="133" spans="2:18">
       <c r="B133" s="105" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D133" s="22">
         <v>0.1</v>
@@ -8758,15 +8745,15 @@
         <v>0.65</v>
       </c>
       <c r="R133" s="56" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="134" spans="2:18">
       <c r="B134" s="106" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C134" s="13" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D134" s="32">
         <v>0.27</v>
@@ -8793,33 +8780,33 @@
         <v>0.41</v>
       </c>
       <c r="L134" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="M134" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="N134" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="O134" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="P134" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="Q134" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="R134" s="56" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="135" spans="2:18">
       <c r="B135" s="107" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D135" s="8">
         <v>0.1</v>
@@ -8854,15 +8841,15 @@
       <c r="P135" s="76"/>
       <c r="Q135" s="77"/>
       <c r="R135" s="56" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="136" spans="2:18">
       <c r="B136" s="108" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D136" s="30">
         <v>0.06</v>
@@ -8897,15 +8884,15 @@
       <c r="P136" s="2"/>
       <c r="Q136" s="78"/>
       <c r="R136" s="56" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="137" spans="2:18">
       <c r="B137" s="109" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C137" s="28" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D137" s="79">
         <v>0.12</v>
@@ -8932,33 +8919,33 @@
         <v>0.26</v>
       </c>
       <c r="L137" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="M137" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="N137" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="O137" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="P137" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="Q137" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="R137" s="56" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="138" spans="2:18">
       <c r="B138" s="109" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C138" s="28" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D138" s="29">
         <v>0.56999999999999995</v>
@@ -8985,33 +8972,33 @@
         <v>1.06</v>
       </c>
       <c r="L138" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="M138" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="N138" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="O138" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="P138" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="Q138" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="R138" s="56" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="139" spans="2:18">
       <c r="B139" s="109" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D139" s="30">
         <v>0.06</v>
@@ -9036,15 +9023,15 @@
       <c r="P139" s="2"/>
       <c r="Q139" s="78"/>
       <c r="R139" s="56" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="140" spans="2:18">
       <c r="B140" s="110" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D140" s="30">
         <v>7.0000000000000007E-2</v>
@@ -9089,15 +9076,15 @@
         <v>0.33</v>
       </c>
       <c r="R140" s="56" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="141" spans="2:18">
       <c r="B141" s="108" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D141" s="30">
         <v>0.02</v>
@@ -9127,30 +9114,30 @@
         <v>0.1</v>
       </c>
       <c r="M141" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="N141" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="O141" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="P141" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="Q141" s="32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="R141" s="56" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="142" spans="2:18" ht="14.65" thickBot="1">
       <c r="B142" s="111" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="D142" s="10">
         <v>0.02</v>
@@ -9195,7 +9182,7 @@
         <v>0.15</v>
       </c>
       <c r="R142" s="58" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="143" spans="2:18" ht="14.65" thickTop="1"/>
@@ -9208,6 +9195,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F24FF01B6E691B418AC7A3AA007394EC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2842777d906afb735552f47e63b23c65">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8f43ef-8ea4-412d-9c18-5388ad596486" xmlns:ns4="c1e77170-3c0a-491c-a033-5a7c184eabd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="352f9ab862d979d0253968f43d118292" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
@@ -9426,7 +9421,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -9435,15 +9430,24 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53964A40-A6D0-45D9-B1D4-1342A31D1BCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35331C5A-856A-46E2-8755-4FFF5881D9DA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9462,27 +9466,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53964A40-A6D0-45D9-B1D4-1342A31D1BCB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="c1e77170-3c0a-491c-a033-5a7c184eabd7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data-source/技能数据.xlsx
+++ b/data-source/技能数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE28897-4E7C-467B-A300-731F754B0B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CBC416-86B8-4147-A1F9-95EB7BD1881C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F03E0F5E-A49D-457A-ADAE-8FAE4055FE2C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="282">
   <si>
     <t>格挡大师</t>
   </si>
@@ -8779,23 +8779,23 @@
       <c r="K134" s="32">
         <v>0.41</v>
       </c>
-      <c r="L134" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="M134" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="N134" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="O134" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="P134" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q134" s="32" t="s">
-        <v>237</v>
+      <c r="L134" s="32">
+        <v>0.43</v>
+      </c>
+      <c r="M134" s="32">
+        <v>0.45</v>
+      </c>
+      <c r="N134" s="32">
+        <v>0.47</v>
+      </c>
+      <c r="O134" s="32">
+        <v>0.49</v>
+      </c>
+      <c r="P134" s="32">
+        <v>0.51</v>
+      </c>
+      <c r="Q134" s="32">
+        <v>0.55000000000000004</v>
       </c>
       <c r="R134" s="56" t="s">
         <v>206</v>
@@ -8918,23 +8918,23 @@
       <c r="K137" s="79">
         <v>0.26</v>
       </c>
-      <c r="L137" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="M137" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="N137" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="O137" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="P137" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q137" s="32" t="s">
-        <v>237</v>
+      <c r="L137" s="32">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M137" s="32">
+        <v>0.3</v>
+      </c>
+      <c r="N137" s="32">
+        <v>0.32</v>
+      </c>
+      <c r="O137" s="32">
+        <v>0.34</v>
+      </c>
+      <c r="P137" s="32">
+        <v>0.36</v>
+      </c>
+      <c r="Q137" s="32">
+        <v>0.4</v>
       </c>
       <c r="R137" s="56" t="s">
         <v>206</v>
@@ -9203,6 +9203,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F24FF01B6E691B418AC7A3AA007394EC" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2842777d906afb735552f47e63b23c65">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c8f43ef-8ea4-412d-9c18-5388ad596486" xmlns:ns4="c1e77170-3c0a-491c-a033-5a7c184eabd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="352f9ab862d979d0253968f43d118292" ns3:_="" ns4:_="">
     <xsd:import namespace="2c8f43ef-8ea4-412d-9c18-5388ad596486"/>
@@ -9421,15 +9430,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53964A40-A6D0-45D9-B1D4-1342A31D1BCB}">
   <ds:schemaRefs>
@@ -9448,6 +9448,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35331C5A-856A-46E2-8755-4FFF5881D9DA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9464,12 +9472,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data-source/技能数据.xlsx
+++ b/data-source/技能数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CBC416-86B8-4147-A1F9-95EB7BD1881C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3FAE45-8B1F-4FDA-B2E9-E06716BFF15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F03E0F5E-A49D-457A-ADAE-8FAE4055FE2C}"/>
   </bookViews>
@@ -1143,9 +1143,6 @@
     <t>熟练的珠宝匠</t>
   </si>
   <si>
-    <t>激活时有1%的几率保留护符的奶就度</t>
-  </si>
-  <si>
     <r>
       <t>减少寒冷伤害</t>
     </r>
@@ -1602,6 +1599,9 @@
       </rPr>
       <t>的几率给护盾瞬间充能</t>
     </r>
+  </si>
+  <si>
+    <t>激活时有1%的几率保留护符的耐久度</t>
   </si>
 </sst>
 </file>
@@ -3176,7 +3176,7 @@
         <v>25</v>
       </c>
       <c r="R2" s="59" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="2:21" ht="41.65">
@@ -3219,7 +3219,7 @@
       <c r="P3" s="35"/>
       <c r="Q3" s="35"/>
       <c r="R3" s="68" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="2:21" ht="41.65">
@@ -3262,7 +3262,7 @@
       <c r="P4" s="35"/>
       <c r="Q4" s="35"/>
       <c r="R4" s="68" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="2:21" ht="41.65">
@@ -3287,7 +3287,7 @@
       <c r="P5" s="53"/>
       <c r="Q5" s="65"/>
       <c r="R5" s="68" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="2:21" ht="41.65">
@@ -3340,7 +3340,7 @@
         <v>90</v>
       </c>
       <c r="R6" s="68" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="2:21">
@@ -3393,7 +3393,7 @@
         <v>4.2</v>
       </c>
       <c r="R7" s="68" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="2:21" ht="41.65">
@@ -3446,7 +3446,7 @@
         <v>36</v>
       </c>
       <c r="R8" s="68" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="2:21" ht="41.65">
@@ -3499,7 +3499,7 @@
         <v>1.2</v>
       </c>
       <c r="R9" s="68" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="2:21" ht="41.65">
@@ -3552,7 +3552,7 @@
         <v>1.2</v>
       </c>
       <c r="R10" s="68" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="2:21">
@@ -3605,7 +3605,7 @@
         <v>15</v>
       </c>
       <c r="R11" s="68" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="2:21">
@@ -3658,7 +3658,7 @@
         <v>0.6</v>
       </c>
       <c r="R12" s="68" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="2:21">
@@ -3711,7 +3711,7 @@
         <v>0.6</v>
       </c>
       <c r="R13" s="68" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="2:21">
@@ -3764,15 +3764,15 @@
         <v>15</v>
       </c>
       <c r="R14" s="68" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="2:21" ht="14.65" thickBot="1">
       <c r="B15" s="84" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" s="57" t="s">
         <v>195</v>
-      </c>
-      <c r="C15" s="57" t="s">
-        <v>196</v>
       </c>
       <c r="D15" s="57">
         <v>2</v>
@@ -3817,7 +3817,7 @@
         <v>15</v>
       </c>
       <c r="R15" s="69" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U15" s="55"/>
     </row>
@@ -3889,7 +3889,7 @@
         <v>25</v>
       </c>
       <c r="R17" s="59" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="2:20">
@@ -3916,7 +3916,7 @@
       <c r="P18" s="35"/>
       <c r="Q18" s="35"/>
       <c r="R18" s="68" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="2:20">
@@ -3945,7 +3945,7 @@
       <c r="P19" s="35"/>
       <c r="Q19" s="35"/>
       <c r="R19" s="68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="2:20">
@@ -3974,7 +3974,7 @@
       <c r="P20" s="35"/>
       <c r="Q20" s="35"/>
       <c r="R20" s="68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="2:20">
@@ -4003,7 +4003,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
       <c r="R21" s="68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="2:20" ht="27.75">
@@ -4034,7 +4034,7 @@
       <c r="P22" s="35"/>
       <c r="Q22" s="35"/>
       <c r="R22" s="68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="2:20" ht="27.75">
@@ -4065,7 +4065,7 @@
       <c r="P23" s="35"/>
       <c r="Q23" s="35"/>
       <c r="R23" s="68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="2:20" ht="27.75">
@@ -4098,7 +4098,7 @@
       <c r="P24" s="35"/>
       <c r="Q24" s="35"/>
       <c r="R24" s="68" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="2:20" ht="27.75">
@@ -4131,7 +4131,7 @@
       <c r="P25" s="35"/>
       <c r="Q25" s="35"/>
       <c r="R25" s="68" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="2:20" ht="27.75">
@@ -4164,7 +4164,7 @@
       <c r="P26" s="35"/>
       <c r="Q26" s="35"/>
       <c r="R26" s="68" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="2:20" ht="27.75">
@@ -4199,7 +4199,7 @@
       <c r="P27" s="35"/>
       <c r="Q27" s="35"/>
       <c r="R27" s="68" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" spans="2:20" ht="27.75">
@@ -4234,7 +4234,7 @@
       <c r="P28" s="35"/>
       <c r="Q28" s="35"/>
       <c r="R28" s="68" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" spans="2:20" ht="27.75">
@@ -4269,7 +4269,7 @@
       <c r="P29" s="35"/>
       <c r="Q29" s="35"/>
       <c r="R29" s="68" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="30" spans="2:20" ht="42" thickBot="1">
@@ -4306,7 +4306,7 @@
       <c r="P30" s="35"/>
       <c r="Q30" s="35"/>
       <c r="R30" s="68" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31" spans="2:20" ht="42" thickBot="1">
@@ -4345,7 +4345,7 @@
       <c r="P31" s="35"/>
       <c r="Q31" s="35"/>
       <c r="R31" s="68" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="T31" s="52"/>
     </row>
@@ -4385,7 +4385,7 @@
       <c r="P32" s="35"/>
       <c r="Q32" s="35"/>
       <c r="R32" s="68" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33" spans="2:18" ht="41.65">
@@ -4424,7 +4424,7 @@
       <c r="P33" s="35"/>
       <c r="Q33" s="35"/>
       <c r="R33" s="68" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" spans="2:18" ht="27.75">
@@ -4465,12 +4465,12 @@
       <c r="P34" s="35"/>
       <c r="Q34" s="35"/>
       <c r="R34" s="68" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="2:18">
       <c r="B35" s="101" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>149</v>
@@ -4518,7 +4518,7 @@
         <v>15</v>
       </c>
       <c r="R35" s="71" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36" spans="2:18" ht="41.65">
@@ -4571,7 +4571,7 @@
         <v>15</v>
       </c>
       <c r="R36" s="68" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" spans="2:18">
@@ -4624,7 +4624,7 @@
         <v>15</v>
       </c>
       <c r="R37" s="71" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="2:18" ht="41.65">
@@ -4677,7 +4677,7 @@
         <v>15</v>
       </c>
       <c r="R38" s="68" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="39" spans="2:18">
@@ -4730,7 +4730,7 @@
         <v>15</v>
       </c>
       <c r="R39" s="71" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="40" spans="2:18">
@@ -4783,7 +4783,7 @@
         <v>15</v>
       </c>
       <c r="R40" s="71" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="41" spans="2:18">
@@ -4836,7 +4836,7 @@
         <v>15</v>
       </c>
       <c r="R41" s="71" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" spans="2:18">
@@ -4844,7 +4844,7 @@
         <v>106</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D42" s="22">
         <v>0.04</v>
@@ -4889,7 +4889,7 @@
         <v>0.3</v>
       </c>
       <c r="R42" s="71" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="43" spans="2:18">
@@ -4897,7 +4897,7 @@
         <v>105</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D43" s="8">
         <v>0.06</v>
@@ -4942,12 +4942,12 @@
         <v>0.4</v>
       </c>
       <c r="R43" s="71" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="44" spans="2:18" ht="14.65" thickBot="1">
       <c r="B44" s="103" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>149</v>
@@ -4995,7 +4995,7 @@
         <v>15</v>
       </c>
       <c r="R44" s="72" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="45" spans="2:18" ht="15" thickTop="1" thickBot="1">
@@ -5066,7 +5066,7 @@
         <v>25</v>
       </c>
       <c r="R46" s="59" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="2:18" ht="42.75">
@@ -5109,7 +5109,7 @@
       <c r="P47" s="35"/>
       <c r="Q47" s="35"/>
       <c r="R47" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="48" spans="2:18" ht="42.75">
@@ -5152,7 +5152,7 @@
       <c r="P48" s="35"/>
       <c r="Q48" s="35"/>
       <c r="R48" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="49" spans="2:18" ht="42.75">
@@ -5195,7 +5195,7 @@
       <c r="P49" s="35"/>
       <c r="Q49" s="35"/>
       <c r="R49" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="50" spans="2:18" ht="42.75">
@@ -5238,7 +5238,7 @@
       <c r="P50" s="35"/>
       <c r="Q50" s="35"/>
       <c r="R50" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="51" spans="2:18" ht="42.75">
@@ -5281,7 +5281,7 @@
       <c r="P51" s="35"/>
       <c r="Q51" s="35"/>
       <c r="R51" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="52" spans="2:18" ht="42.75">
@@ -5324,7 +5324,7 @@
       <c r="P52" s="35"/>
       <c r="Q52" s="35"/>
       <c r="R52" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="53" spans="2:18" ht="42.75">
@@ -5367,7 +5367,7 @@
       <c r="P53" s="35"/>
       <c r="Q53" s="35"/>
       <c r="R53" s="73" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="54" spans="2:18" ht="42.75">
@@ -5410,7 +5410,7 @@
       <c r="P54" s="35"/>
       <c r="Q54" s="35"/>
       <c r="R54" s="73" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="55" spans="2:18">
@@ -5418,7 +5418,7 @@
         <v>95</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D55" s="6">
         <v>4</v>
@@ -5445,7 +5445,7 @@
       <c r="P55" s="35"/>
       <c r="Q55" s="35"/>
       <c r="R55" s="71" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="56" spans="2:18">
@@ -5453,7 +5453,7 @@
         <v>94</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D56" s="6">
         <v>4</v>
@@ -5480,7 +5480,7 @@
       <c r="P56" s="35"/>
       <c r="Q56" s="35"/>
       <c r="R56" s="71" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="57" spans="2:18">
@@ -5488,7 +5488,7 @@
         <v>93</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D57" s="6">
         <v>4</v>
@@ -5515,7 +5515,7 @@
       <c r="P57" s="35"/>
       <c r="Q57" s="35"/>
       <c r="R57" s="71" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="2:18" ht="14.65" thickBot="1">
@@ -5523,7 +5523,7 @@
         <v>92</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D58" s="18">
         <v>4</v>
@@ -5550,7 +5550,7 @@
       <c r="P58" s="48"/>
       <c r="Q58" s="48"/>
       <c r="R58" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="59" spans="2:18" ht="15" thickTop="1" thickBot="1">
@@ -5621,7 +5621,7 @@
         <v>25</v>
       </c>
       <c r="R60" s="59" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" spans="2:18" ht="28.5">
@@ -5664,7 +5664,7 @@
       <c r="P61" s="35"/>
       <c r="Q61" s="35"/>
       <c r="R61" s="73" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="62" spans="2:18" ht="28.5">
@@ -5707,7 +5707,7 @@
       <c r="P62" s="35"/>
       <c r="Q62" s="35"/>
       <c r="R62" s="73" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="63" spans="2:18" ht="28.5">
@@ -5750,7 +5750,7 @@
       <c r="P63" s="35"/>
       <c r="Q63" s="35"/>
       <c r="R63" s="73" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="64" spans="2:18" ht="28.5">
@@ -5793,7 +5793,7 @@
       <c r="P64" s="35"/>
       <c r="Q64" s="35"/>
       <c r="R64" s="73" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="65" spans="2:18" ht="28.5">
@@ -5836,7 +5836,7 @@
       <c r="P65" s="35"/>
       <c r="Q65" s="35"/>
       <c r="R65" s="73" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="66" spans="2:18" ht="28.5">
@@ -5879,7 +5879,7 @@
       <c r="P66" s="35"/>
       <c r="Q66" s="35"/>
       <c r="R66" s="73" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" spans="2:18" ht="28.5">
@@ -5922,7 +5922,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="35"/>
       <c r="R67" s="73" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68" spans="2:18">
@@ -5965,7 +5965,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="35"/>
       <c r="R68" s="71" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="69" spans="2:18">
@@ -6008,7 +6008,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
       <c r="R69" s="71" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70" spans="2:18">
@@ -6051,7 +6051,7 @@
       <c r="P70" s="35"/>
       <c r="Q70" s="35"/>
       <c r="R70" s="71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="71" spans="2:18">
@@ -6094,7 +6094,7 @@
       <c r="P71" s="35"/>
       <c r="Q71" s="35"/>
       <c r="R71" s="71" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="72" spans="2:18">
@@ -6137,7 +6137,7 @@
       <c r="P72" s="35"/>
       <c r="Q72" s="35"/>
       <c r="R72" s="71" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="73" spans="2:18">
@@ -6180,7 +6180,7 @@
       <c r="P73" s="35"/>
       <c r="Q73" s="35"/>
       <c r="R73" s="71" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="74" spans="2:18">
@@ -6223,7 +6223,7 @@
       <c r="P74" s="35"/>
       <c r="Q74" s="35"/>
       <c r="R74" s="71" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="75" spans="2:18">
@@ -6266,7 +6266,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="35"/>
       <c r="R75" s="71" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="76" spans="2:18">
@@ -6309,7 +6309,7 @@
       <c r="P76" s="35"/>
       <c r="Q76" s="35"/>
       <c r="R76" s="71" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="77" spans="2:18">
@@ -6352,7 +6352,7 @@
       <c r="P77" s="35"/>
       <c r="Q77" s="35"/>
       <c r="R77" s="71" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78" spans="2:18">
@@ -6395,7 +6395,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
       <c r="R78" s="71" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="79" spans="2:18">
@@ -6403,7 +6403,7 @@
         <v>72</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D79" s="6">
         <v>2</v>
@@ -6438,7 +6438,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
       <c r="R79" s="71" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="80" spans="2:18">
@@ -6481,7 +6481,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
       <c r="R80" s="71" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="81" spans="2:18">
@@ -6524,7 +6524,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
       <c r="R81" s="71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="82" spans="2:18">
@@ -6567,7 +6567,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
       <c r="R82" s="71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="83" spans="2:18">
@@ -6610,7 +6610,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
       <c r="R83" s="71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="84" spans="2:18">
@@ -6653,7 +6653,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
       <c r="R84" s="71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="85" spans="2:18" ht="28.5">
@@ -6696,7 +6696,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
       <c r="R85" s="73" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="86" spans="2:18" ht="28.5">
@@ -6739,7 +6739,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
       <c r="R86" s="73" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="87" spans="2:18" ht="28.5">
@@ -6782,7 +6782,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
       <c r="R87" s="73" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="88" spans="2:18">
@@ -6825,7 +6825,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
       <c r="R88" s="71" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="89" spans="2:18">
@@ -6868,7 +6868,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
       <c r="R89" s="71" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" spans="2:18">
@@ -6911,7 +6911,7 @@
       <c r="P90" s="35"/>
       <c r="Q90" s="35"/>
       <c r="R90" s="71" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="91" spans="2:18">
@@ -6954,7 +6954,7 @@
       <c r="P91" s="35"/>
       <c r="Q91" s="35"/>
       <c r="R91" s="71" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="92" spans="2:18">
@@ -6997,7 +6997,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
       <c r="R92" s="71" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="93" spans="2:18">
@@ -7040,7 +7040,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
       <c r="R93" s="71" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="94" spans="2:18">
@@ -7083,12 +7083,12 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
       <c r="R94" s="71" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="95" spans="2:18">
       <c r="B95" s="95" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C95" s="13" t="s">
         <v>56</v>
@@ -7126,7 +7126,7 @@
       <c r="P95" s="35"/>
       <c r="Q95" s="35"/>
       <c r="R95" s="71" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="2:18">
@@ -7169,7 +7169,7 @@
       <c r="P96" s="35"/>
       <c r="Q96" s="35"/>
       <c r="R96" s="71" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="97" spans="2:18" ht="14.65" thickBot="1">
@@ -7212,7 +7212,7 @@
       <c r="P97" s="48"/>
       <c r="Q97" s="48"/>
       <c r="R97" s="72" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="98" spans="2:18" ht="15" thickTop="1" thickBot="1"/>
@@ -7266,7 +7266,7 @@
         <v>25</v>
       </c>
       <c r="R99" s="59" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="100" spans="2:18" ht="42.75">
@@ -7309,7 +7309,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
       <c r="R100" s="73" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="101" spans="2:18">
@@ -7352,7 +7352,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
       <c r="R101" s="71" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="102" spans="2:18" ht="42.75">
@@ -7395,7 +7395,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
       <c r="R102" s="73" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="103" spans="2:18" ht="42.75">
@@ -7438,7 +7438,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
       <c r="R103" s="73" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="104" spans="2:18">
@@ -7481,7 +7481,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
       <c r="R104" s="71" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="105" spans="2:18" ht="42.75">
@@ -7524,7 +7524,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
       <c r="R105" s="73" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="106" spans="2:18" ht="43.15" thickBot="1">
@@ -7567,7 +7567,7 @@
       <c r="P106" s="48"/>
       <c r="Q106" s="48"/>
       <c r="R106" s="74" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="107" spans="2:18" ht="15" thickTop="1" thickBot="1"/>
@@ -7621,7 +7621,7 @@
         <v>25</v>
       </c>
       <c r="R108" s="59" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="109" spans="2:18" ht="42.75">
@@ -7664,7 +7664,7 @@
       <c r="P109" s="4"/>
       <c r="Q109" s="43"/>
       <c r="R109" s="73" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="110" spans="2:18" ht="42.75">
@@ -7717,7 +7717,7 @@
         <v>30</v>
       </c>
       <c r="R110" s="73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="111" spans="2:18" ht="42.75">
@@ -7760,7 +7760,7 @@
       <c r="P111" s="4"/>
       <c r="Q111" s="43"/>
       <c r="R111" s="73" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="112" spans="2:18" ht="28.5">
@@ -7803,7 +7803,7 @@
       <c r="P112" s="4"/>
       <c r="Q112" s="43"/>
       <c r="R112" s="73" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="113" spans="2:20" ht="42.75">
@@ -7846,7 +7846,7 @@
       <c r="P113" s="5"/>
       <c r="Q113" s="45"/>
       <c r="R113" s="73" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="114" spans="2:20" ht="42.75">
@@ -7889,7 +7889,7 @@
       <c r="P114" s="4"/>
       <c r="Q114" s="43"/>
       <c r="R114" s="73" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="115" spans="2:20">
@@ -7942,7 +7942,7 @@
         <v>0.5</v>
       </c>
       <c r="R115" s="71" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="116" spans="2:20">
@@ -7995,7 +7995,7 @@
         <v>0.3</v>
       </c>
       <c r="R116" s="71" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="117" spans="2:20">
@@ -8048,7 +8048,7 @@
         <v>0.15</v>
       </c>
       <c r="R117" s="71" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="118" spans="2:20" ht="14.65" thickBot="1">
@@ -8056,7 +8056,7 @@
         <v>11</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D118" s="22">
         <v>0.02</v>
@@ -8101,7 +8101,7 @@
         <v>0.15</v>
       </c>
       <c r="R118" s="71" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="119" spans="2:20" ht="14.65" thickBot="1">
@@ -8109,7 +8109,7 @@
         <v>145</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D119" s="22">
         <v>0.02</v>
@@ -8154,7 +8154,7 @@
         <v>0.15</v>
       </c>
       <c r="R119" s="71" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T119" s="52"/>
     </row>
@@ -8163,7 +8163,7 @@
         <v>19</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D120" s="22">
         <v>0.08</v>
@@ -8198,7 +8198,7 @@
       <c r="P120" s="35"/>
       <c r="Q120" s="47"/>
       <c r="R120" s="71" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="121" spans="2:20" ht="14.65" thickBot="1">
@@ -8206,7 +8206,7 @@
         <v>18</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D121" s="26">
         <v>0.08</v>
@@ -8241,7 +8241,7 @@
       <c r="P121" s="48"/>
       <c r="Q121" s="49"/>
       <c r="R121" s="72" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="122" spans="2:20" ht="15" thickTop="1" thickBot="1"/>
@@ -8295,7 +8295,7 @@
         <v>25</v>
       </c>
       <c r="R123" s="59" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="124" spans="2:20" ht="42.75">
@@ -8338,7 +8338,7 @@
       <c r="P124" s="4"/>
       <c r="Q124" s="43"/>
       <c r="R124" s="63" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="125" spans="2:20" ht="28.5">
@@ -8381,7 +8381,7 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="43"/>
       <c r="R125" s="63" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="126" spans="2:20" ht="28.5">
@@ -8424,7 +8424,7 @@
       <c r="P126" s="4"/>
       <c r="Q126" s="43"/>
       <c r="R126" s="63" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="127" spans="2:20">
@@ -8467,7 +8467,7 @@
       <c r="P127" s="4"/>
       <c r="Q127" s="43"/>
       <c r="R127" s="56" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="128" spans="2:20">
@@ -8475,7 +8475,7 @@
         <v>15</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D128" s="22">
         <v>0.04</v>
@@ -8500,7 +8500,7 @@
       <c r="P128" s="4"/>
       <c r="Q128" s="43"/>
       <c r="R128" s="56" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="129" spans="2:18">
@@ -8543,7 +8543,7 @@
       <c r="P129" s="4"/>
       <c r="Q129" s="43"/>
       <c r="R129" s="56" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="130" spans="2:18">
@@ -8586,7 +8586,7 @@
       <c r="P130" s="4"/>
       <c r="Q130" s="43"/>
       <c r="R130" s="56" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="131" spans="2:18">
@@ -8639,7 +8639,7 @@
         <v>15</v>
       </c>
       <c r="R131" s="56" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="132" spans="2:18">
@@ -8647,7 +8647,7 @@
         <v>8</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D132" s="22">
         <v>0.06</v>
@@ -8692,7 +8692,7 @@
         <v>0.2</v>
       </c>
       <c r="R132" s="56" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="133" spans="2:18">
@@ -8745,7 +8745,7 @@
         <v>0.65</v>
       </c>
       <c r="R133" s="56" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="134" spans="2:18">
@@ -8798,7 +8798,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="R134" s="56" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="135" spans="2:18">
@@ -8841,7 +8841,7 @@
       <c r="P135" s="76"/>
       <c r="Q135" s="77"/>
       <c r="R135" s="56" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="136" spans="2:18">
@@ -8884,7 +8884,7 @@
       <c r="P136" s="2"/>
       <c r="Q136" s="78"/>
       <c r="R136" s="56" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="137" spans="2:18">
@@ -8937,7 +8937,7 @@
         <v>0.4</v>
       </c>
       <c r="R137" s="56" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="138" spans="2:18">
@@ -8972,25 +8972,25 @@
         <v>1.06</v>
       </c>
       <c r="L138" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M138" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N138" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O138" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P138" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q138" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="R138" s="56" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="139" spans="2:18">
@@ -9023,7 +9023,7 @@
       <c r="P139" s="2"/>
       <c r="Q139" s="78"/>
       <c r="R139" s="56" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="140" spans="2:18">
@@ -9031,7 +9031,7 @@
         <v>1</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D140" s="30">
         <v>7.0000000000000007E-2</v>
@@ -9076,7 +9076,7 @@
         <v>0.33</v>
       </c>
       <c r="R140" s="56" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="141" spans="2:18">
@@ -9084,7 +9084,7 @@
         <v>187</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>188</v>
+        <v>281</v>
       </c>
       <c r="D141" s="30">
         <v>0.02</v>
@@ -9114,22 +9114,22 @@
         <v>0.1</v>
       </c>
       <c r="M141" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N141" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O141" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="P141" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q141" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="R141" s="56" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="2:18" ht="14.65" thickBot="1">
@@ -9137,7 +9137,7 @@
         <v>0</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D142" s="10">
         <v>0.02</v>
@@ -9182,7 +9182,7 @@
         <v>0.15</v>
       </c>
       <c r="R142" s="58" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="143" spans="2:18" ht="14.65" thickTop="1"/>
@@ -9195,20 +9195,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c1e77170-3c0a-491c-a033-5a7c184eabd7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9431,6 +9431,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53964A40-A6D0-45D9-B1D4-1342A31D1BCB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -9443,14 +9451,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F26B4FE2-AECD-489D-B504-AE0180E73AAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data-source/技能数据.xlsx
+++ b/data-source/技能数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3FAE45-8B1F-4FDA-B2E9-E06716BFF15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0F40DA-5D01-4065-8F9C-6BE7AE2EAF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F03E0F5E-A49D-457A-ADAE-8FAE4055FE2C}"/>
   </bookViews>
@@ -1300,9 +1300,6 @@
     <t>Lv1-Lv10：游商/酷吏地下城</t>
   </si>
   <si>
-    <t>Lv1-Lv5：酷吏地下城；</t>
-  </si>
-  <si>
     <t>Lv1-Lv10：酷吏地下城；</t>
   </si>
   <si>
@@ -1331,9 +1328,6 @@
   </si>
   <si>
     <t>Lv1-Lv5：4级图；Lv1-Lv7：5级图/城堡；Lv6-Lv10：酷吏地下城；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv5：酷吏地下城；Lv1-Lv6：被诅咒的天文台</t>
   </si>
   <si>
     <t>Lv1-Lv4：4级图；Lv1-Lv8：5级图/城堡；Lv5-Lv10：大车炮台；Lv6-Lv10：酷吏地下城</t>
@@ -1469,15 +1463,6 @@
     <t>Lv1-Lv4：死亡村庄/破损大车/堕落骑士；Lv1-Lv10: 古人墓穴/大车炮台/被弃者地下城/大型被弃者地窖；</t>
   </si>
   <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：哈利德/哈特/弗拉格纳/被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：哈利德/哈特/弗拉格纳/被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；Lv1-Lv10：被诅咒的天文台</t>
-  </si>
-  <si>
-    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；</t>
-  </si>
-  <si>
     <t>Lv1-Lv2：墓地之夜/小型被弃者地窖；Lv1-Lv4：1-3级图/被弃者地窖；Lv4-Lv5：酷吏地下城/叛徒地下墓穴/继母艾莎；Lv1-Lv5：被弃者地下城/地下神祠/大型被弃者地窖；Lv1-Lv6：哈利德/哈特/弗拉格纳；Lv5-Lv6：4级图/5级图/城堡；</t>
   </si>
   <si>
@@ -1602,6 +1587,21 @@
   </si>
   <si>
     <t>激活时有1%的几率保留护符的耐久度</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：酷吏地下城；Lv1-Lv6：商店购买</t>
+  </si>
+  <si>
+    <t>Lv1-Lv5：酷吏地下城；Lv1-Lv6：被诅咒的天文台/商店购买</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：哈利德/哈特/弗拉格纳/被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；Lv1-Lv10：商店购买</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：哈利德/哈特/弗拉格纳/被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；Lv1-Lv10：被诅咒的天文台/商店购买</t>
+  </si>
+  <si>
+    <t>Lv1-Lv2：小型被弃者地窖；Lv1-Lv3：1-3级图/墓地之夜/被弃者地窖；Lv3-Lv5：被弃者地下城/叛徒地下墓穴/继母艾莎/大型被弃者地窖；Lv4-Lv5：4级图；Lv1-Lv5：哈利德/哈特/弗拉格纳/地下神祠；Lv5-Lv6：5级图/城堡；Lv3-Lv10：酷吏地下城；Lv1-Lv10：商店购买</t>
   </si>
 </sst>
 </file>
@@ -3219,7 +3219,7 @@
       <c r="P3" s="35"/>
       <c r="Q3" s="35"/>
       <c r="R3" s="68" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="2:21" ht="41.65">
@@ -3262,7 +3262,7 @@
       <c r="P4" s="35"/>
       <c r="Q4" s="35"/>
       <c r="R4" s="68" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="2:21" ht="41.65">
@@ -3287,7 +3287,7 @@
       <c r="P5" s="53"/>
       <c r="Q5" s="65"/>
       <c r="R5" s="68" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="2:21" ht="41.65">
@@ -3340,7 +3340,7 @@
         <v>90</v>
       </c>
       <c r="R6" s="68" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="2:21">
@@ -3446,7 +3446,7 @@
         <v>36</v>
       </c>
       <c r="R8" s="68" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="2:21" ht="41.65">
@@ -3499,7 +3499,7 @@
         <v>1.2</v>
       </c>
       <c r="R9" s="68" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" spans="2:21" ht="41.65">
@@ -3552,7 +3552,7 @@
         <v>1.2</v>
       </c>
       <c r="R10" s="68" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="2:21">
@@ -3605,7 +3605,7 @@
         <v>15</v>
       </c>
       <c r="R11" s="68" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" spans="2:21">
@@ -3916,7 +3916,7 @@
       <c r="P18" s="35"/>
       <c r="Q18" s="35"/>
       <c r="R18" s="68" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" spans="2:20">
@@ -3945,7 +3945,7 @@
       <c r="P19" s="35"/>
       <c r="Q19" s="35"/>
       <c r="R19" s="68" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="2:20">
@@ -3974,7 +3974,7 @@
       <c r="P20" s="35"/>
       <c r="Q20" s="35"/>
       <c r="R20" s="68" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="2:20">
@@ -4003,7 +4003,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
       <c r="R21" s="68" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="2:20" ht="27.75">
@@ -4034,7 +4034,7 @@
       <c r="P22" s="35"/>
       <c r="Q22" s="35"/>
       <c r="R22" s="68" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="2:20" ht="27.75">
@@ -4065,7 +4065,7 @@
       <c r="P23" s="35"/>
       <c r="Q23" s="35"/>
       <c r="R23" s="68" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="2:20" ht="27.75">
@@ -4098,7 +4098,7 @@
       <c r="P24" s="35"/>
       <c r="Q24" s="35"/>
       <c r="R24" s="68" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="2:20" ht="27.75">
@@ -4131,7 +4131,7 @@
       <c r="P25" s="35"/>
       <c r="Q25" s="35"/>
       <c r="R25" s="68" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="2:20" ht="27.75">
@@ -4164,7 +4164,7 @@
       <c r="P26" s="35"/>
       <c r="Q26" s="35"/>
       <c r="R26" s="68" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="2:20" ht="27.75">
@@ -4199,7 +4199,7 @@
       <c r="P27" s="35"/>
       <c r="Q27" s="35"/>
       <c r="R27" s="68" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" spans="2:20" ht="27.75">
@@ -4234,7 +4234,7 @@
       <c r="P28" s="35"/>
       <c r="Q28" s="35"/>
       <c r="R28" s="68" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="2:20" ht="27.75">
@@ -4269,7 +4269,7 @@
       <c r="P29" s="35"/>
       <c r="Q29" s="35"/>
       <c r="R29" s="68" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" spans="2:20" ht="42" thickBot="1">
@@ -4306,7 +4306,7 @@
       <c r="P30" s="35"/>
       <c r="Q30" s="35"/>
       <c r="R30" s="68" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" spans="2:20" ht="42" thickBot="1">
@@ -4345,7 +4345,7 @@
       <c r="P31" s="35"/>
       <c r="Q31" s="35"/>
       <c r="R31" s="68" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="T31" s="52"/>
     </row>
@@ -4385,7 +4385,7 @@
       <c r="P32" s="35"/>
       <c r="Q32" s="35"/>
       <c r="R32" s="68" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="2:18" ht="41.65">
@@ -4424,7 +4424,7 @@
       <c r="P33" s="35"/>
       <c r="Q33" s="35"/>
       <c r="R33" s="68" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="34" spans="2:18" ht="27.75">
@@ -4465,7 +4465,7 @@
       <c r="P34" s="35"/>
       <c r="Q34" s="35"/>
       <c r="R34" s="68" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="35" spans="2:18">
@@ -4571,7 +4571,7 @@
         <v>15</v>
       </c>
       <c r="R36" s="68" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="37" spans="2:18">
@@ -4624,7 +4624,7 @@
         <v>15</v>
       </c>
       <c r="R37" s="71" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="2:18" ht="41.65">
@@ -4677,7 +4677,7 @@
         <v>15</v>
       </c>
       <c r="R38" s="68" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="39" spans="2:18">
@@ -4730,7 +4730,7 @@
         <v>15</v>
       </c>
       <c r="R39" s="71" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" spans="2:18">
@@ -4783,7 +4783,7 @@
         <v>15</v>
       </c>
       <c r="R40" s="71" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="2:18">
@@ -4836,7 +4836,7 @@
         <v>15</v>
       </c>
       <c r="R41" s="71" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="2:18">
@@ -4889,7 +4889,7 @@
         <v>0.3</v>
       </c>
       <c r="R42" s="71" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="43" spans="2:18">
@@ -4942,7 +4942,7 @@
         <v>0.4</v>
       </c>
       <c r="R43" s="71" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="44" spans="2:18" ht="14.65" thickBot="1">
@@ -5109,7 +5109,7 @@
       <c r="P47" s="35"/>
       <c r="Q47" s="35"/>
       <c r="R47" s="73" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="48" spans="2:18" ht="42.75">
@@ -5152,7 +5152,7 @@
       <c r="P48" s="35"/>
       <c r="Q48" s="35"/>
       <c r="R48" s="73" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="49" spans="2:18" ht="42.75">
@@ -5195,7 +5195,7 @@
       <c r="P49" s="35"/>
       <c r="Q49" s="35"/>
       <c r="R49" s="73" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50" spans="2:18" ht="42.75">
@@ -5238,7 +5238,7 @@
       <c r="P50" s="35"/>
       <c r="Q50" s="35"/>
       <c r="R50" s="73" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="51" spans="2:18" ht="42.75">
@@ -5281,7 +5281,7 @@
       <c r="P51" s="35"/>
       <c r="Q51" s="35"/>
       <c r="R51" s="73" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="52" spans="2:18" ht="42.75">
@@ -5324,7 +5324,7 @@
       <c r="P52" s="35"/>
       <c r="Q52" s="35"/>
       <c r="R52" s="73" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53" spans="2:18" ht="42.75">
@@ -5367,7 +5367,7 @@
       <c r="P53" s="35"/>
       <c r="Q53" s="35"/>
       <c r="R53" s="73" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54" spans="2:18" ht="42.75">
@@ -5410,7 +5410,7 @@
       <c r="P54" s="35"/>
       <c r="Q54" s="35"/>
       <c r="R54" s="73" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
     </row>
     <row r="55" spans="2:18">
@@ -5445,7 +5445,7 @@
       <c r="P55" s="35"/>
       <c r="Q55" s="35"/>
       <c r="R55" s="71" t="s">
-        <v>215</v>
+        <v>277</v>
       </c>
     </row>
     <row r="56" spans="2:18">
@@ -5480,7 +5480,7 @@
       <c r="P56" s="35"/>
       <c r="Q56" s="35"/>
       <c r="R56" s="71" t="s">
-        <v>226</v>
+        <v>278</v>
       </c>
     </row>
     <row r="57" spans="2:18">
@@ -5515,7 +5515,7 @@
       <c r="P57" s="35"/>
       <c r="Q57" s="35"/>
       <c r="R57" s="71" t="s">
-        <v>215</v>
+        <v>277</v>
       </c>
     </row>
     <row r="58" spans="2:18" ht="14.65" thickBot="1">
@@ -5550,7 +5550,7 @@
       <c r="P58" s="48"/>
       <c r="Q58" s="48"/>
       <c r="R58" s="72" t="s">
-        <v>215</v>
+        <v>277</v>
       </c>
     </row>
     <row r="59" spans="2:18" ht="15" thickTop="1" thickBot="1">
@@ -5664,7 +5664,7 @@
       <c r="P61" s="35"/>
       <c r="Q61" s="35"/>
       <c r="R61" s="73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="62" spans="2:18" ht="28.5">
@@ -5707,7 +5707,7 @@
       <c r="P62" s="35"/>
       <c r="Q62" s="35"/>
       <c r="R62" s="73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="63" spans="2:18" ht="28.5">
@@ -5750,7 +5750,7 @@
       <c r="P63" s="35"/>
       <c r="Q63" s="35"/>
       <c r="R63" s="73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="64" spans="2:18" ht="28.5">
@@ -5793,7 +5793,7 @@
       <c r="P64" s="35"/>
       <c r="Q64" s="35"/>
       <c r="R64" s="73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="65" spans="2:18" ht="28.5">
@@ -5836,7 +5836,7 @@
       <c r="P65" s="35"/>
       <c r="Q65" s="35"/>
       <c r="R65" s="73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="66" spans="2:18" ht="28.5">
@@ -5879,7 +5879,7 @@
       <c r="P66" s="35"/>
       <c r="Q66" s="35"/>
       <c r="R66" s="73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="2:18" ht="28.5">
@@ -5922,7 +5922,7 @@
       <c r="P67" s="35"/>
       <c r="Q67" s="35"/>
       <c r="R67" s="73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="68" spans="2:18">
@@ -5965,7 +5965,7 @@
       <c r="P68" s="35"/>
       <c r="Q68" s="35"/>
       <c r="R68" s="71" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="69" spans="2:18">
@@ -6008,7 +6008,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
       <c r="R69" s="71" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="70" spans="2:18">
@@ -6051,7 +6051,7 @@
       <c r="P70" s="35"/>
       <c r="Q70" s="35"/>
       <c r="R70" s="71" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="2:18">
@@ -6094,7 +6094,7 @@
       <c r="P71" s="35"/>
       <c r="Q71" s="35"/>
       <c r="R71" s="71" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="72" spans="2:18">
@@ -6137,7 +6137,7 @@
       <c r="P72" s="35"/>
       <c r="Q72" s="35"/>
       <c r="R72" s="71" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="73" spans="2:18">
@@ -6180,7 +6180,7 @@
       <c r="P73" s="35"/>
       <c r="Q73" s="35"/>
       <c r="R73" s="71" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="74" spans="2:18">
@@ -6223,7 +6223,7 @@
       <c r="P74" s="35"/>
       <c r="Q74" s="35"/>
       <c r="R74" s="71" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="75" spans="2:18">
@@ -6266,7 +6266,7 @@
       <c r="P75" s="35"/>
       <c r="Q75" s="35"/>
       <c r="R75" s="71" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="76" spans="2:18">
@@ -6309,7 +6309,7 @@
       <c r="P76" s="35"/>
       <c r="Q76" s="35"/>
       <c r="R76" s="71" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="77" spans="2:18">
@@ -6352,7 +6352,7 @@
       <c r="P77" s="35"/>
       <c r="Q77" s="35"/>
       <c r="R77" s="71" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="78" spans="2:18">
@@ -6395,7 +6395,7 @@
       <c r="P78" s="35"/>
       <c r="Q78" s="35"/>
       <c r="R78" s="71" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="79" spans="2:18">
@@ -6403,7 +6403,7 @@
         <v>72</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D79" s="6">
         <v>2</v>
@@ -6438,7 +6438,7 @@
       <c r="P79" s="35"/>
       <c r="Q79" s="35"/>
       <c r="R79" s="71" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="80" spans="2:18">
@@ -6481,7 +6481,7 @@
       <c r="P80" s="35"/>
       <c r="Q80" s="35"/>
       <c r="R80" s="71" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="81" spans="2:18">
@@ -6524,7 +6524,7 @@
       <c r="P81" s="35"/>
       <c r="Q81" s="35"/>
       <c r="R81" s="71" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="82" spans="2:18">
@@ -6567,7 +6567,7 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
       <c r="R82" s="71" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="83" spans="2:18">
@@ -6610,7 +6610,7 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
       <c r="R83" s="71" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="84" spans="2:18">
@@ -6653,7 +6653,7 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
       <c r="R84" s="71" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="85" spans="2:18" ht="28.5">
@@ -6696,7 +6696,7 @@
       <c r="P85" s="35"/>
       <c r="Q85" s="35"/>
       <c r="R85" s="73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="2:18" ht="28.5">
@@ -6739,7 +6739,7 @@
       <c r="P86" s="35"/>
       <c r="Q86" s="35"/>
       <c r="R86" s="73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="87" spans="2:18" ht="28.5">
@@ -6782,7 +6782,7 @@
       <c r="P87" s="35"/>
       <c r="Q87" s="35"/>
       <c r="R87" s="73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="88" spans="2:18">
@@ -6825,7 +6825,7 @@
       <c r="P88" s="35"/>
       <c r="Q88" s="35"/>
       <c r="R88" s="71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="89" spans="2:18">
@@ -6868,7 +6868,7 @@
       <c r="P89" s="35"/>
       <c r="Q89" s="35"/>
       <c r="R89" s="71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="90" spans="2:18">
@@ -6997,7 +6997,7 @@
       <c r="P92" s="35"/>
       <c r="Q92" s="35"/>
       <c r="R92" s="71" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="93" spans="2:18">
@@ -7040,7 +7040,7 @@
       <c r="P93" s="35"/>
       <c r="Q93" s="35"/>
       <c r="R93" s="71" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="94" spans="2:18">
@@ -7083,7 +7083,7 @@
       <c r="P94" s="35"/>
       <c r="Q94" s="35"/>
       <c r="R94" s="71" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="95" spans="2:18">
@@ -7309,7 +7309,7 @@
       <c r="P100" s="35"/>
       <c r="Q100" s="35"/>
       <c r="R100" s="73" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="101" spans="2:18">
@@ -7352,7 +7352,7 @@
       <c r="P101" s="35"/>
       <c r="Q101" s="35"/>
       <c r="R101" s="71" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="102" spans="2:18" ht="42.75">
@@ -7395,7 +7395,7 @@
       <c r="P102" s="35"/>
       <c r="Q102" s="35"/>
       <c r="R102" s="73" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="103" spans="2:18" ht="42.75">
@@ -7438,7 +7438,7 @@
       <c r="P103" s="35"/>
       <c r="Q103" s="35"/>
       <c r="R103" s="73" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="104" spans="2:18">
@@ -7481,7 +7481,7 @@
       <c r="P104" s="35"/>
       <c r="Q104" s="35"/>
       <c r="R104" s="71" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="105" spans="2:18" ht="42.75">
@@ -7524,7 +7524,7 @@
       <c r="P105" s="35"/>
       <c r="Q105" s="35"/>
       <c r="R105" s="73" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="106" spans="2:18" ht="43.15" thickBot="1">
@@ -7567,7 +7567,7 @@
       <c r="P106" s="48"/>
       <c r="Q106" s="48"/>
       <c r="R106" s="74" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="107" spans="2:18" ht="15" thickTop="1" thickBot="1"/>
@@ -7664,7 +7664,7 @@
       <c r="P109" s="4"/>
       <c r="Q109" s="43"/>
       <c r="R109" s="73" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="110" spans="2:18" ht="42.75">
@@ -7717,7 +7717,7 @@
         <v>30</v>
       </c>
       <c r="R110" s="73" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="111" spans="2:18" ht="42.75">
@@ -7760,7 +7760,7 @@
       <c r="P111" s="4"/>
       <c r="Q111" s="43"/>
       <c r="R111" s="73" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="112" spans="2:18" ht="28.5">
@@ -7803,7 +7803,7 @@
       <c r="P112" s="4"/>
       <c r="Q112" s="43"/>
       <c r="R112" s="73" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="113" spans="2:20" ht="42.75">
@@ -7846,7 +7846,7 @@
       <c r="P113" s="5"/>
       <c r="Q113" s="45"/>
       <c r="R113" s="73" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="114" spans="2:20" ht="42.75">
@@ -7889,7 +7889,7 @@
       <c r="P114" s="4"/>
       <c r="Q114" s="43"/>
       <c r="R114" s="73" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="115" spans="2:20">
@@ -7942,7 +7942,7 @@
         <v>0.5</v>
       </c>
       <c r="R115" s="71" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="116" spans="2:20">
@@ -8163,7 +8163,7 @@
         <v>19</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D120" s="22">
         <v>0.08</v>
@@ -8198,7 +8198,7 @@
       <c r="P120" s="35"/>
       <c r="Q120" s="47"/>
       <c r="R120" s="71" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="121" spans="2:20" ht="14.65" thickBot="1">
@@ -8206,7 +8206,7 @@
         <v>18</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D121" s="26">
         <v>0.08</v>
@@ -8241,7 +8241,7 @@
       <c r="P121" s="48"/>
       <c r="Q121" s="49"/>
       <c r="R121" s="72" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="122" spans="2:20" ht="15" thickTop="1" thickBot="1"/>
@@ -8338,7 +8338,7 @@
       <c r="P124" s="4"/>
       <c r="Q124" s="43"/>
       <c r="R124" s="63" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="125" spans="2:20" ht="28.5">
@@ -8381,7 +8381,7 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="43"/>
       <c r="R125" s="63" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="126" spans="2:20" ht="28.5">
@@ -8424,7 +8424,7 @@
       <c r="P126" s="4"/>
       <c r="Q126" s="43"/>
       <c r="R126" s="63" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="127" spans="2:20">
@@ -8467,7 +8467,7 @@
       <c r="P127" s="4"/>
       <c r="Q127" s="43"/>
       <c r="R127" s="56" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="128" spans="2:20">
@@ -8475,7 +8475,7 @@
         <v>15</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="D128" s="22">
         <v>0.04</v>
@@ -8500,7 +8500,7 @@
       <c r="P128" s="4"/>
       <c r="Q128" s="43"/>
       <c r="R128" s="56" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="129" spans="2:18">
@@ -8543,7 +8543,7 @@
       <c r="P129" s="4"/>
       <c r="Q129" s="43"/>
       <c r="R129" s="56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="130" spans="2:18">
@@ -8586,7 +8586,7 @@
       <c r="P130" s="4"/>
       <c r="Q130" s="43"/>
       <c r="R130" s="56" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="131" spans="2:18">
@@ -8647,7 +8647,7 @@
         <v>8</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="D132" s="22">
         <v>0.06</v>
@@ -8692,7 +8692,7 @@
         <v>0.2</v>
       </c>
       <c r="R132" s="56" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="133" spans="2:18">
@@ -8841,7 +8841,7 @@
       <c r="P135" s="76"/>
       <c r="Q135" s="77"/>
       <c r="R135" s="56" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="136" spans="2:18">
@@ -8972,22 +8972,22 @@
         <v>1.06</v>
       </c>
       <c r="L138" s="32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M138" s="32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="N138" s="32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="O138" s="32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P138" s="32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q138" s="32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="R138" s="56" t="s">
         <v>205</v>
@@ -9023,7 +9023,7 @@
       <c r="P139" s="2"/>
       <c r="Q139" s="78"/>
       <c r="R139" s="56" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="140" spans="2:18">
@@ -9084,7 +9084,7 @@
         <v>187</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D141" s="30">
         <v>0.02</v>
@@ -9114,19 +9114,19 @@
         <v>0.1</v>
       </c>
       <c r="M141" s="32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="N141" s="32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="O141" s="32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P141" s="32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q141" s="32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="R141" s="56" t="s">
         <v>209</v>
@@ -9137,7 +9137,7 @@
         <v>0</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D142" s="10">
         <v>0.02</v>
@@ -9182,7 +9182,7 @@
         <v>0.15</v>
       </c>
       <c r="R142" s="58" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="143" spans="2:18" ht="14.65" thickTop="1"/>
